--- a/output/bkg pending - PW DEPOT CO., LTD.xlsx
+++ b/output/bkg pending - PW DEPOT CO., LTD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pending" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AI$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AI$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI42"/>
+  <dimension ref="A1:AI34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -730,24 +730,20 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260702326</t>
+          <t>HASLS22260701768</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>SWSR</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>202609172200</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr"/>
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
@@ -756,74 +752,73 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260805</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>THAI POLYCARBONATE CO., LTD.</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>THAI POLYCARBONATE CO., LTD.</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>POLYCARBONATE RESIN , HS CODEIS 3907.40</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>PLEASE PROVIDE GOOD AND CLEAN CONTAINER, NO RUST, NO HOLE, NO SMELL WITH STRONG FLOORBOARD (LOAD BY FORKLIFT) AND BULLET SEAL TO THIS SHIPMENT</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-08-27, Return : 2026-08-28
-**CHECK OPENGATE BEFORE RETURN CNTR**</t>
+          <t>CY CNTR DD.05/08/2026 RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="O3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="Y3" s="4" t="n">
         <v>0</v>
@@ -872,24 +867,20 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260702337</t>
+          <t>HASLS22260701770</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>DJCF</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>0151N</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>202609192000</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -898,52 +889,52 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260806</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>SDS-ACUTECH CO., LTD.</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>3AC (THAILAND) CO., LTD.</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>AIR PURIFIER</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-08, Return : 2026-09-08</t>
+          <t>CY CNTR DD.06/08/2026 RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" s="4" t="n">
         <v>0</v>
@@ -964,7 +955,7 @@
         <v>0</v>
       </c>
       <c r="X4" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y4" s="4" t="n">
         <v>0</v>
@@ -1013,24 +1004,20 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260800725</t>
+          <t>HASLS22260800165</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>202609202300</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -1039,73 +1026,73 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>JPKSM</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x4 </t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>PANDA GOGO LOGISTICS CO., LTD.</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>GC-M PTA COMPANY LIMITED</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>PURIFIED TEREPHTHALIC ACID (HS CODE: 291736)</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>SPECIAL REQUEST : STANDARD CONTAINERS</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>[FIX]Pickup : 2026-09-09, Return : 2026-09-10</t>
+          <t>CY CNTR DD.13/08/2026 RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="O5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="Y5" s="4" t="n">
         <v>0</v>
@@ -1154,22 +1141,22 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260800736</t>
+          <t>HASLS22260800512</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>202609240000</t>
+          <t>202609182100</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -1180,32 +1167,32 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x3 </t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>SDS-ACUTECH CO., LTD.</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>3AC (THAILAND) CO., LTD.</t>
+          <t>THAI SYNTHETIC RUBBERS CO., LTD.</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>AIR PURIFIER</t>
+          <t>POLYBUTADIENE RUBBER</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -1215,19 +1202,18 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-08, Return : 2026-09-08 
-** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER **
-</t>
+          <t>CY-RTN : 12-13/09/2026 RQST GOOD CONDITION : GRADE B+
+REF : ID-N015914</t>
         </is>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="4" t="n">
         <v>0</v>
@@ -1297,22 +1283,22 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260800958</t>
+          <t>HASLS22260800577</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SWBT</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>202609210630</t>
+          <t>202609220500</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -1323,52 +1309,52 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 20'x20 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>20260907</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>WHA GC LOGISTICS COMPANY LIMITED</t>
+          <t>TRUE MARINE CO., LTD.</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>INOAC (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>POLYURETHANE FOAM</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+          <t>**REQUEST GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>CY 07/09/26 , RTN 11/09/26</t>
+          <t>Pickup : 2026-09-12, Return : 2026-09-14 (1ST RETURN 16/09/26)</t>
         </is>
       </c>
       <c r="O7" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R7" s="4" t="n">
         <v>0</v>
@@ -1438,12 +1424,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260800960</t>
+          <t>HASLS22260800725</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>PGPO</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1453,7 +1439,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>202609220100</t>
+          <t>202609202300</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -1464,12 +1450,12 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPKSM</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 20'x20 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1479,37 +1465,37 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>WHA GC LOGISTICS COMPANY LIMITED</t>
+          <t>PANDA GOGO LOGISTICS CO., LTD.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>GC-M PTA COMPANY LIMITED</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>PURIFIED TEREPHTHALIC ACID (HS CODE: 291736)</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+          <t>SPECIAL REQUEST : STANDARD CONTAINERS</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>CY 09/09/26 , RTN 13/09/26</t>
+          <t>[FIX]Pickup : 2026-09-09, Return : 2026-09-10</t>
         </is>
       </c>
       <c r="O8" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="P8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R8" s="4" t="n">
         <v>0</v>
@@ -1579,22 +1565,22 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801116</t>
+          <t>HASLS22260800885</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>202609211500</t>
+          <t>202609240000</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -1605,187 +1591,189 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x5 </t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MARITIME ALLIANCE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>GUARDIAN INDUSTRIES CORP LTD.</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>GLASS &amp; GLASS PRODUCTS</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>REQ LOAD UNDERDECK
+GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>Pickup : 2026-09-10, Return : 2026-09-11
+**CHECK OPENGATE BEFORE RETURN CNTR**</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="4">
+        <f>SUM(O9:W9)-X9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="4">
+        <f>MAX(0,O9-MAX(0,X9))</f>
+        <v/>
+      </c>
+      <c r="AB9" s="4">
+        <f>MAX(0,P9-MAX(0,X9-SUM(O9:O9)))</f>
+        <v/>
+      </c>
+      <c r="AC9" s="4">
+        <f>MAX(0,Q9-MAX(0,X9-SUM(O9:P9)))</f>
+        <v/>
+      </c>
+      <c r="AD9" s="4">
+        <f>MAX(0,R9-MAX(0,X9-SUM(O9:Q9)))</f>
+        <v/>
+      </c>
+      <c r="AE9" s="4">
+        <f>MAX(0,S9-MAX(0,X9-SUM(O9:R9)))</f>
+        <v/>
+      </c>
+      <c r="AF9" s="4">
+        <f>MAX(0,T9-MAX(0,X9-SUM(O9:S9)))</f>
+        <v/>
+      </c>
+      <c r="AG9" s="4">
+        <f>MAX(0,U9-MAX(0,X9-SUM(O9:T9)))</f>
+        <v/>
+      </c>
+      <c r="AH9" s="4">
+        <f>MAX(0,V9-MAX(0,X9-SUM(O9:U9)))</f>
+        <v/>
+      </c>
+      <c r="AI9" s="4">
+        <f>MAX(0,W9-MAX(0,X9-SUM(O9:V9)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260801116</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>KJT</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>202609212300</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
           <t>CNSHK</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>20260810</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>THAI POLYCARBONATE CO., LTD.</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>THAI POLYCARBONATE CO., LTD.</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>POLYCARBONATE RESIN (HS CODE. 3907.40)</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>Loading with pallet-by forklift, required good container with strong floorboard and bullet seal to this shipment</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Pickup : 2026-08-10, Return : 2026-08-14 
  ** PLEASE CHECK OPEN GATE BEFORE RETURN CNTR **
 </t>
         </is>
       </c>
-      <c r="O9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="4">
-        <f>SUM(O9:W9)-X9</f>
-        <v/>
-      </c>
-      <c r="AA9" s="4">
-        <f>MAX(0,O9-MAX(0,X9))</f>
-        <v/>
-      </c>
-      <c r="AB9" s="4">
-        <f>MAX(0,P9-MAX(0,X9-SUM(O9:O9)))</f>
-        <v/>
-      </c>
-      <c r="AC9" s="4">
-        <f>MAX(0,Q9-MAX(0,X9-SUM(O9:P9)))</f>
-        <v/>
-      </c>
-      <c r="AD9" s="4">
-        <f>MAX(0,R9-MAX(0,X9-SUM(O9:Q9)))</f>
-        <v/>
-      </c>
-      <c r="AE9" s="4">
-        <f>MAX(0,S9-MAX(0,X9-SUM(O9:R9)))</f>
-        <v/>
-      </c>
-      <c r="AF9" s="4">
-        <f>MAX(0,T9-MAX(0,X9-SUM(O9:S9)))</f>
-        <v/>
-      </c>
-      <c r="AG9" s="4">
-        <f>MAX(0,U9-MAX(0,X9-SUM(O9:T9)))</f>
-        <v/>
-      </c>
-      <c r="AH9" s="4">
-        <f>MAX(0,V9-MAX(0,X9-SUM(O9:U9)))</f>
-        <v/>
-      </c>
-      <c r="AI9" s="4">
-        <f>MAX(0,W9-MAX(0,X9-SUM(O9:V9)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260801451</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>ICVY</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>2607S</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>202609191300</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>20260907</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>CONNEXT LOG (THAILAND) CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>HIMILE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>TIRE MOLD</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>REQUEST: NO HOLE, NO SMELL, STRONG BOARD</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>Pickup : 2026-09-07, Return : 2026-09-08</t>
-        </is>
-      </c>
       <c r="O10" s="4" t="n">
         <v>1</v>
       </c>
@@ -1863,22 +1851,22 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801665</t>
+          <t>HASLS22260801636</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>202609150600</t>
+          <t>202609212300</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -1889,27 +1877,27 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPIWK</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>SCGJWD LOGISTICS PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1919,16 +1907,18 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>RQST NO RED WALL CONTAINER,CLEAN CONTAINER NO OIL STAINS , NO RUSTY ,NO CUT OR HOLE</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-02, Return : 2026-09-08</t>
+          <t xml:space="preserve">CY-RTN : 11-14/09/2026
+IVN : 3031060556
+NO RED WALL CONTAINER,CLEAN CONTAINER NO OIL STAINS , NO RUSTY ,NO CUT OR HOLE    </t>
         </is>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11" s="4" t="n">
         <v>0</v>
@@ -2004,22 +1994,22 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801667</t>
+          <t>HASLS22260801908</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>202609150600</t>
+          <t>202609212300</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -2030,7 +2020,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPOSA</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -2040,32 +2030,33 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>GLOBAL GREEN CHEMICALS PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>GLOBAL GREEN CHEMICALS PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t xml:space="preserve">REFINED GLYCERINE 99.5% USP </t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>Stowage Under Deck Away from Boiler</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-02, Return : 2026-09-08</t>
+          <t>Pickup : 2026-09-10, Return : 2026-09-12 
+** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER **</t>
         </is>
       </c>
       <c r="O12" s="4" t="n">
@@ -2145,22 +2136,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801668</t>
+          <t>HASLS22260801918</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>202609150600</t>
+          <t>202609212300</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -2171,46 +2162,46 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x3 </t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>THAI POLYCARBONATE CO., LTD.</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>THAI POLYCARBONATE CO., LTD.</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>POLYCARBONATE RESIN , HS CODEIS 3907.40</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>PLEASE PROVIDE GOOD AND CLEAN CONTAINER, NO RUST, NO HOLE, NO SMELL WITH STRONG FLOORBOARD (LOAD BY FORKLIFT) AND BULLET SEAL TO THIS SHIPMENT</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-02, Return : 2026-09-08</t>
+          <t>Pickup : 2026-09-10, Return : 2026-09-11</t>
         </is>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0</v>
@@ -2286,22 +2277,22 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801712</t>
+          <t>HASLS22260801978</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SWCP</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>202609121200</t>
+          <t>202609232100</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -2312,52 +2303,52 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>L.A.1 CO.,LTD.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>TANATEX CHEMICALS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>CHEMICALS PRODUCT (NON DG)</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>REQUEST : CONTAINER MAX GROSS 32.50 TONS</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-01, Return : 2026-09-08</t>
+          <t>Pickup : 2026-09-08, Return : 2026-09-09</t>
         </is>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14" s="4" t="n">
         <v>0</v>
@@ -2427,22 +2418,22 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801713</t>
+          <t>HASLS22260801983</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SWCP</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>202609121200</t>
+          <t>202609232100</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -2453,7 +2444,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -2463,32 +2454,32 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>L.A.1 CO.,LTD.</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>TANATEX CHEMICALS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>CHEMICALS PRODUCT (NON DG)</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-01, Return : 2026-09-08</t>
+          <t>Pickup : 2026-09-08, Return : 2026-09-09</t>
         </is>
       </c>
       <c r="O15" s="4" t="n">
@@ -2568,22 +2559,22 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801714</t>
+          <t>HASLS22260801987</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>SWCP</t>
+          <t>KMSU</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>202609121200</t>
+          <t>202610011600</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -2594,46 +2585,46 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260822</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>L.A.1 CO.,LTD.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>TANATEX CHEMICALS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>CHEMICALS PRODUCT (NON DG)</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-01, Return : 2026-09-08</t>
+          <t>Pickup : 2026-08-22, Return : 2026-08-24</t>
         </is>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>0</v>
@@ -2709,22 +2700,22 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801715</t>
+          <t>HASLS22260802005</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>SWCP</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>202609121200</t>
+          <t>202609202300</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -2735,46 +2726,47 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x3 </t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>THAI POLYCARBONATE CO., LTD.</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>THAI POLYCARBONATE CO., LTD.</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>POLYCARBONATE RESIN (HS CODE. 3907.40)</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>Loading with pallet-by forklift, required good container with strong floorboard and bullet seal to this shipment***</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-01, Return : 2026-09-08</t>
+          <t>Pickup : 2026-09-11, Return : 2026-09-15 
+ ** PLEASE CHECK OPEN GATE BEFORE RETURN CNTR **</t>
         </is>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>0</v>
@@ -2850,22 +2842,22 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801718</t>
+          <t>HASLS22260802006</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>SWCP</t>
+          <t>KMTP</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>202609121200</t>
+          <t>202609202300</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -2876,46 +2868,46 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>THAI POLYCARBONATE CO., LTD.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>THAI POLYCARBONATE CO., LTD.</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>POLYCARBONATE RESIN (HS CODE. 3907.40)</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>Loading with pallet-by forklift, required good container with strong floorboard and bullet seal to this shipment***</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-01, Return : 2026-09-08</t>
+          <t>Pickup : 2026-09-11, Return : 2026-09-15</t>
         </is>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>0</v>
@@ -2991,22 +2983,22 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801719</t>
+          <t>HASLS22260802314</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>SWCP</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>202609121200</t>
+          <t>202609220500</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -3027,7 +3019,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>20260901</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -3052,7 +3044,8 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-01, Return : 2026-09-08</t>
+          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-15 
+** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER ** </t>
         </is>
       </c>
       <c r="O19" s="4" t="n">
@@ -3132,22 +3125,22 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801720</t>
+          <t>HASLS22260802316</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>202609150600</t>
+          <t>202609220500</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -3158,7 +3151,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -3168,7 +3161,7 @@
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -3193,7 +3186,8 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-02, Return : 2026-09-08</t>
+          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-15
+** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER **  </t>
         </is>
       </c>
       <c r="O20" s="4" t="n">
@@ -3273,22 +3267,22 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801721</t>
+          <t>HASLS22260802317</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>202609150600</t>
+          <t>202609220500</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -3299,7 +3293,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -3309,7 +3303,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -3334,7 +3328,8 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-02, Return : 2026-09-08</t>
+          <t>Pickup : 2026-09-09, Return : 2026-09-15 
+** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER **</t>
         </is>
       </c>
       <c r="O21" s="4" t="n">
@@ -3414,22 +3409,22 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801723</t>
+          <t>HASLS22260802319</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2607N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>202609150600</t>
+          <t>202609220500</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -3440,7 +3435,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -3450,7 +3445,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>20260902</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -3475,7 +3470,8 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-02, Return : 2026-09-08</t>
+          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-15
+** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER ** </t>
         </is>
       </c>
       <c r="O22" s="4" t="n">
@@ -3555,22 +3551,22 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801978</t>
+          <t>HASLS22260802321</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>202609222100</t>
+          <t>202609220500</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -3581,52 +3577,53 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>L.A.1 CO.,LTD.</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>TANATEX CHEMICALS (THAILAND) CO., LTD.</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>CHEMICALS PRODUCT (NON DG)</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>REQUEST : CONTAINER MAX GROSS 32.50 TONS</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-08, Return : 2026-09-09</t>
+          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-15 
+** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER ** </t>
         </is>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R23" s="4" t="n">
         <v>0</v>
@@ -3696,22 +3693,22 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801983</t>
+          <t>HASLS22260802322</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>202609222100</t>
+          <t>202609220500</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -3722,7 +3719,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -3732,32 +3729,33 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>L.A.1 CO.,LTD.</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>TANATEX CHEMICALS (THAILAND) CO., LTD.</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>CHEMICALS PRODUCT (NON DG)</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-08, Return : 2026-09-09</t>
+          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-15 
+** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER ** </t>
         </is>
       </c>
       <c r="O24" s="4" t="n">
@@ -3837,22 +3835,22 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801987</t>
+          <t>HASLS22260802323</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>KMSU</t>
+          <t>SWBT</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>202609301500</t>
+          <t>202609221100</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -3863,46 +3861,47 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>20260822</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>L.A.1 CO.,LTD.</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>TANATEX CHEMICALS (THAILAND) CO., LTD.</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>CHEMICALS PRODUCT (NON DG)</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-08-22, Return : 2026-08-24</t>
+          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-15 
+** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER ** </t>
         </is>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>0</v>
@@ -3978,22 +3977,22 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802228</t>
+          <t>HASLS22260802325</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWBT</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>202609202300</t>
+          <t>202609221100</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -4004,7 +4003,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -4019,30 +4018,28 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>DOUBLE A (1991) PUBLIC COMPANY LIMITED</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>DOUBLE A (1991) PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>PAPER</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CY-RTN : 09-14/09/2026
-REF : PI-HK-TH-DA-26090001
-FRE $ 35, FREE TIME 14/14 , DTHC(HKD)2000
-</t>
+          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-15
+** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER ** </t>
         </is>
       </c>
       <c r="O26" s="4" t="n">
@@ -4122,22 +4119,22 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802314</t>
+          <t>HASLS22260802326</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWBT</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>202609230700</t>
+          <t>202609221100</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -4148,7 +4145,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -4183,7 +4180,7 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-15 
+          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-15
 ** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER ** </t>
         </is>
       </c>
@@ -4264,7 +4261,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802316</t>
+          <t>HASLS22260802337</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -4279,7 +4276,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>202609230700</t>
+          <t>202609220500</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -4290,27 +4287,27 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>JPTYO</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>WHA GC LOGISTICS COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -4320,23 +4317,22 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-15
-** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER **  </t>
+          <t xml:space="preserve">CY-RTN 10-13/09/26 </t>
         </is>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R28" s="4" t="n">
         <v>0</v>
@@ -4406,7 +4402,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802317</t>
+          <t>HASLS22260802338</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -4421,7 +4417,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>202609230700</t>
+          <t>202609220500</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -4432,27 +4428,27 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>JPTYO</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>WHA GC LOGISTICS COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -4462,23 +4458,22 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>Pickup : 2026-09-09, Return : 2026-09-15 
-** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER **</t>
+          <t xml:space="preserve">CY-RTN 10-13/09/26 </t>
         </is>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R29" s="4" t="n">
         <v>0</v>
@@ -4548,22 +4543,22 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802319</t>
+          <t>HASLS22260802387</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>202609230700</t>
+          <t>202609251600</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -4574,27 +4569,27 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx8 </t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>SCGJWD LOGISTICS PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -4604,23 +4599,24 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-15
-** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER ** </t>
+          <t xml:space="preserve">CY-RTN :11-15/09/2026 *INV : 3031061381*
+REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY
+</t>
         </is>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R30" s="4" t="n">
         <v>0</v>
@@ -4690,7 +4686,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802321</t>
+          <t>HASLS22260900048</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -4705,7 +4701,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>202609230700</t>
+          <t>202609220500</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -4716,7 +4712,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>JPHKT</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -4726,17 +4722,17 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>WHA GC LOGISTICS COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -4746,13 +4742,12 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-15 
-** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER ** </t>
+          <t>CY-RTN 12-14/09/26 (PR2610001572)</t>
         </is>
       </c>
       <c r="O31" s="4" t="n">
@@ -4832,22 +4827,22 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802322</t>
+          <t>HASLS22260900276</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>202609230700</t>
+          <t>202609240000</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -4858,7 +4853,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -4868,33 +4863,34 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>POLYAMIDE RESIN</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>RQST CNTR SOUND AND CLEAN</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-15 
-** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER ** </t>
+          <t>CY-RTN : 08-10/09/2026
+REF : SAP 2002054403
+RQST CNTR SOUND AND CLEAN</t>
         </is>
       </c>
       <c r="O32" s="4" t="n">
@@ -4974,22 +4970,22 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802323</t>
+          <t>HASLS22260900944</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>SWBT</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2607N</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>202609210630</t>
+          <t>202609151800</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -5000,7 +4996,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -5010,33 +5006,33 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260912</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>TOSHIBA LOGISTICS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>TCFG COMPRESSOR (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t xml:space="preserve">COMPRESSOR </t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-15 
-** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER ** </t>
+          <t>Pickup : 2026-09-12, Return : 2026-09-13
+CLS TIME DD.14/09/2026  @ 23.59</t>
         </is>
       </c>
       <c r="O33" s="4" t="n">
@@ -5114,1246 +5110,108 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260802325</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>SWBT</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>202609210630</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>JPNGO</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>1X20' SEABULK</t>
-        </is>
-      </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-15
-** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER ** </t>
-        </is>
-      </c>
-      <c r="O34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="4">
-        <f>SUM(O34:W34)-X34</f>
-        <v/>
-      </c>
-      <c r="AA34" s="4">
-        <f>MAX(0,O34-MAX(0,X34))</f>
-        <v/>
-      </c>
-      <c r="AB34" s="4">
-        <f>MAX(0,P34-MAX(0,X34-SUM(O34:O34)))</f>
-        <v/>
-      </c>
-      <c r="AC34" s="4">
-        <f>MAX(0,Q34-MAX(0,X34-SUM(O34:P34)))</f>
-        <v/>
-      </c>
-      <c r="AD34" s="4">
-        <f>MAX(0,R34-MAX(0,X34-SUM(O34:Q34)))</f>
-        <v/>
-      </c>
-      <c r="AE34" s="4">
-        <f>MAX(0,S34-MAX(0,X34-SUM(O34:R34)))</f>
-        <v/>
-      </c>
-      <c r="AF34" s="4">
-        <f>MAX(0,T34-MAX(0,X34-SUM(O34:S34)))</f>
-        <v/>
-      </c>
-      <c r="AG34" s="4">
-        <f>MAX(0,U34-MAX(0,X34-SUM(O34:T34)))</f>
-        <v/>
-      </c>
-      <c r="AH34" s="4">
-        <f>MAX(0,V34-MAX(0,X34-SUM(O34:U34)))</f>
-        <v/>
-      </c>
-      <c r="AI34" s="4">
-        <f>MAX(0,W34-MAX(0,X34-SUM(O34:V34)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260802326</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>SWBT</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>202609210630</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>JPNGO</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>1X20' SEABULK</t>
-        </is>
-      </c>
-      <c r="N35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pickup : 2026-09-09, Return : 2026-09-15
-** PLEASE CHECK OPEN GATE BEFORE RETURN CONTAINER ** </t>
-        </is>
-      </c>
-      <c r="O35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="4">
-        <f>SUM(O35:W35)-X35</f>
-        <v/>
-      </c>
-      <c r="AA35" s="4">
-        <f>MAX(0,O35-MAX(0,X35))</f>
-        <v/>
-      </c>
-      <c r="AB35" s="4">
-        <f>MAX(0,P35-MAX(0,X35-SUM(O35:O35)))</f>
-        <v/>
-      </c>
-      <c r="AC35" s="4">
-        <f>MAX(0,Q35-MAX(0,X35-SUM(O35:P35)))</f>
-        <v/>
-      </c>
-      <c r="AD35" s="4">
-        <f>MAX(0,R35-MAX(0,X35-SUM(O35:Q35)))</f>
-        <v/>
-      </c>
-      <c r="AE35" s="4">
-        <f>MAX(0,S35-MAX(0,X35-SUM(O35:R35)))</f>
-        <v/>
-      </c>
-      <c r="AF35" s="4">
-        <f>MAX(0,T35-MAX(0,X35-SUM(O35:S35)))</f>
-        <v/>
-      </c>
-      <c r="AG35" s="4">
-        <f>MAX(0,U35-MAX(0,X35-SUM(O35:T35)))</f>
-        <v/>
-      </c>
-      <c r="AH35" s="4">
-        <f>MAX(0,V35-MAX(0,X35-SUM(O35:U35)))</f>
-        <v/>
-      </c>
-      <c r="AI35" s="4">
-        <f>MAX(0,W35-MAX(0,X35-SUM(O35:V35)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260802440</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>2614N</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>202609242200</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>DOUBLE A (1991) PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>DOUBLE A (1991) PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>PAPER</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="N36" s="4" t="inlineStr">
-        <is>
-          <t>CY-RTN : 09-18/09/2026
-REF : PI-HK-TH-DA-26090014
-FRT $ 35 , FREE TIME 14/14, DTHC (HKD) 2000</t>
-        </is>
-      </c>
-      <c r="O36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="4">
-        <f>SUM(O36:W36)-X36</f>
-        <v/>
-      </c>
-      <c r="AA36" s="4">
-        <f>MAX(0,O36-MAX(0,X36))</f>
-        <v/>
-      </c>
-      <c r="AB36" s="4">
-        <f>MAX(0,P36-MAX(0,X36-SUM(O36:O36)))</f>
-        <v/>
-      </c>
-      <c r="AC36" s="4">
-        <f>MAX(0,Q36-MAX(0,X36-SUM(O36:P36)))</f>
-        <v/>
-      </c>
-      <c r="AD36" s="4">
-        <f>MAX(0,R36-MAX(0,X36-SUM(O36:Q36)))</f>
-        <v/>
-      </c>
-      <c r="AE36" s="4">
-        <f>MAX(0,S36-MAX(0,X36-SUM(O36:R36)))</f>
-        <v/>
-      </c>
-      <c r="AF36" s="4">
-        <f>MAX(0,T36-MAX(0,X36-SUM(O36:S36)))</f>
-        <v/>
-      </c>
-      <c r="AG36" s="4">
-        <f>MAX(0,U36-MAX(0,X36-SUM(O36:T36)))</f>
-        <v/>
-      </c>
-      <c r="AH36" s="4">
-        <f>MAX(0,V36-MAX(0,X36-SUM(O36:U36)))</f>
-        <v/>
-      </c>
-      <c r="AI36" s="4">
-        <f>MAX(0,W36-MAX(0,X36-SUM(O36:V36)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900094</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>KMTP</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>202609202300</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>DOUBLE A (1991) PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>DOUBLE A (1991) PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>PAPER</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="N37" s="4" t="inlineStr">
-        <is>
-          <t>CY-RTN : 09-14/09/2026
-REF : AA-HK-PHO09-0190-26
-FRT $35 , FREE TIME 14/14, DTHB (HKD) 2000</t>
-        </is>
-      </c>
-      <c r="O37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="4">
-        <f>SUM(O37:W37)-X37</f>
-        <v/>
-      </c>
-      <c r="AA37" s="4">
-        <f>MAX(0,O37-MAX(0,X37))</f>
-        <v/>
-      </c>
-      <c r="AB37" s="4">
-        <f>MAX(0,P37-MAX(0,X37-SUM(O37:O37)))</f>
-        <v/>
-      </c>
-      <c r="AC37" s="4">
-        <f>MAX(0,Q37-MAX(0,X37-SUM(O37:P37)))</f>
-        <v/>
-      </c>
-      <c r="AD37" s="4">
-        <f>MAX(0,R37-MAX(0,X37-SUM(O37:Q37)))</f>
-        <v/>
-      </c>
-      <c r="AE37" s="4">
-        <f>MAX(0,S37-MAX(0,X37-SUM(O37:R37)))</f>
-        <v/>
-      </c>
-      <c r="AF37" s="4">
-        <f>MAX(0,T37-MAX(0,X37-SUM(O37:S37)))</f>
-        <v/>
-      </c>
-      <c r="AG37" s="4">
-        <f>MAX(0,U37-MAX(0,X37-SUM(O37:T37)))</f>
-        <v/>
-      </c>
-      <c r="AH37" s="4">
-        <f>MAX(0,V37-MAX(0,X37-SUM(O37:U37)))</f>
-        <v/>
-      </c>
-      <c r="AI37" s="4">
-        <f>MAX(0,W37-MAX(0,X37-SUM(O37:V37)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900276</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>202609240000</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>POLYAMIDE RESIN</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="inlineStr">
-        <is>
-          <t>RQST CNTR SOUND AND CLEAN</t>
-        </is>
-      </c>
-      <c r="N38" s="4" t="inlineStr">
-        <is>
-          <t>CY-RTN : 08-10/09/2026
-REF : SAP 2002054403
-RQST CNTR SOUND AND CLEAN</t>
-        </is>
-      </c>
-      <c r="O38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="4">
-        <f>SUM(O38:W38)-X38</f>
-        <v/>
-      </c>
-      <c r="AA38" s="4">
-        <f>MAX(0,O38-MAX(0,X38))</f>
-        <v/>
-      </c>
-      <c r="AB38" s="4">
-        <f>MAX(0,P38-MAX(0,X38-SUM(O38:O38)))</f>
-        <v/>
-      </c>
-      <c r="AC38" s="4">
-        <f>MAX(0,Q38-MAX(0,X38-SUM(O38:P38)))</f>
-        <v/>
-      </c>
-      <c r="AD38" s="4">
-        <f>MAX(0,R38-MAX(0,X38-SUM(O38:Q38)))</f>
-        <v/>
-      </c>
-      <c r="AE38" s="4">
-        <f>MAX(0,S38-MAX(0,X38-SUM(O38:R38)))</f>
-        <v/>
-      </c>
-      <c r="AF38" s="4">
-        <f>MAX(0,T38-MAX(0,X38-SUM(O38:S38)))</f>
-        <v/>
-      </c>
-      <c r="AG38" s="4">
-        <f>MAX(0,U38-MAX(0,X38-SUM(O38:T38)))</f>
-        <v/>
-      </c>
-      <c r="AH38" s="4">
-        <f>MAX(0,V38-MAX(0,X38-SUM(O38:U38)))</f>
-        <v/>
-      </c>
-      <c r="AI38" s="4">
-        <f>MAX(0,W38-MAX(0,X38-SUM(O38:V38)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900277</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>YSVY</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>2607N</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>202609150600</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>20260908</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>POLYAMIDE RESIN</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
-        <is>
-          <t>RQST CNTR SOUND AND CLEAN</t>
-        </is>
-      </c>
-      <c r="N39" s="4" t="inlineStr">
-        <is>
-          <t>CY-RTN : 08-10/09/2026
-REF : SAP 2002054276
-RQST CNTR SOUND AND CLEAN</t>
-        </is>
-      </c>
-      <c r="O39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="4">
-        <f>SUM(O39:W39)-X39</f>
-        <v/>
-      </c>
-      <c r="AA39" s="4">
-        <f>MAX(0,O39-MAX(0,X39))</f>
-        <v/>
-      </c>
-      <c r="AB39" s="4">
-        <f>MAX(0,P39-MAX(0,X39-SUM(O39:O39)))</f>
-        <v/>
-      </c>
-      <c r="AC39" s="4">
-        <f>MAX(0,Q39-MAX(0,X39-SUM(O39:P39)))</f>
-        <v/>
-      </c>
-      <c r="AD39" s="4">
-        <f>MAX(0,R39-MAX(0,X39-SUM(O39:Q39)))</f>
-        <v/>
-      </c>
-      <c r="AE39" s="4">
-        <f>MAX(0,S39-MAX(0,X39-SUM(O39:R39)))</f>
-        <v/>
-      </c>
-      <c r="AF39" s="4">
-        <f>MAX(0,T39-MAX(0,X39-SUM(O39:S39)))</f>
-        <v/>
-      </c>
-      <c r="AG39" s="4">
-        <f>MAX(0,U39-MAX(0,X39-SUM(O39:T39)))</f>
-        <v/>
-      </c>
-      <c r="AH39" s="4">
-        <f>MAX(0,V39-MAX(0,X39-SUM(O39:U39)))</f>
-        <v/>
-      </c>
-      <c r="AI39" s="4">
-        <f>MAX(0,W39-MAX(0,X39-SUM(O39:V39)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900482</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>202609240000</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x18 </t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>WHA GC LOGISTICS COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
-        </is>
-      </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>CY 09/09/26 , RTN 14/09/26</t>
-        </is>
-      </c>
-      <c r="O40" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="P40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="4">
-        <f>SUM(O40:W40)-X40</f>
-        <v/>
-      </c>
-      <c r="AA40" s="4">
-        <f>MAX(0,O40-MAX(0,X40))</f>
-        <v/>
-      </c>
-      <c r="AB40" s="4">
-        <f>MAX(0,P40-MAX(0,X40-SUM(O40:O40)))</f>
-        <v/>
-      </c>
-      <c r="AC40" s="4">
-        <f>MAX(0,Q40-MAX(0,X40-SUM(O40:P40)))</f>
-        <v/>
-      </c>
-      <c r="AD40" s="4">
-        <f>MAX(0,R40-MAX(0,X40-SUM(O40:Q40)))</f>
-        <v/>
-      </c>
-      <c r="AE40" s="4">
-        <f>MAX(0,S40-MAX(0,X40-SUM(O40:R40)))</f>
-        <v/>
-      </c>
-      <c r="AF40" s="4">
-        <f>MAX(0,T40-MAX(0,X40-SUM(O40:S40)))</f>
-        <v/>
-      </c>
-      <c r="AG40" s="4">
-        <f>MAX(0,U40-MAX(0,X40-SUM(O40:T40)))</f>
-        <v/>
-      </c>
-      <c r="AH40" s="4">
-        <f>MAX(0,V40-MAX(0,X40-SUM(O40:U40)))</f>
-        <v/>
-      </c>
-      <c r="AI40" s="4">
-        <f>MAX(0,W40-MAX(0,X40-SUM(O40:V40)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260900483</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>DJCF</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>0151N</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>202609192000</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx4 </t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>20260909</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>WHA GC LOGISTICS COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
-        </is>
-      </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>CY 09/09/26 , RTN 14/09/26</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="4">
-        <f>SUM(O41:W41)-X41</f>
-        <v/>
-      </c>
-      <c r="AA41" s="4">
-        <f>MAX(0,O41-MAX(0,X41))</f>
-        <v/>
-      </c>
-      <c r="AB41" s="4">
-        <f>MAX(0,P41-MAX(0,X41-SUM(O41:O41)))</f>
-        <v/>
-      </c>
-      <c r="AC41" s="4">
-        <f>MAX(0,Q41-MAX(0,X41-SUM(O41:P41)))</f>
-        <v/>
-      </c>
-      <c r="AD41" s="4">
-        <f>MAX(0,R41-MAX(0,X41-SUM(O41:Q41)))</f>
-        <v/>
-      </c>
-      <c r="AE41" s="4">
-        <f>MAX(0,S41-MAX(0,X41-SUM(O41:R41)))</f>
-        <v/>
-      </c>
-      <c r="AF41" s="4">
-        <f>MAX(0,T41-MAX(0,X41-SUM(O41:S41)))</f>
-        <v/>
-      </c>
-      <c r="AG41" s="4">
-        <f>MAX(0,U41-MAX(0,X41-SUM(O41:T41)))</f>
-        <v/>
-      </c>
-      <c r="AH41" s="4">
-        <f>MAX(0,V41-MAX(0,X41-SUM(O41:U41)))</f>
-        <v/>
-      </c>
-      <c r="AI41" s="4">
-        <f>MAX(0,W41-MAX(0,X41-SUM(O41:V41)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="n"/>
-      <c r="O42" s="5">
-        <f>SUM(O3:O41)</f>
-        <v/>
-      </c>
-      <c r="P42" s="5">
-        <f>SUM(P3:P41)</f>
-        <v/>
-      </c>
-      <c r="Q42" s="5">
-        <f>SUM(Q3:Q41)</f>
-        <v/>
-      </c>
-      <c r="R42" s="5">
-        <f>SUM(R3:R41)</f>
-        <v/>
-      </c>
-      <c r="S42" s="5">
-        <f>SUM(S3:S41)</f>
-        <v/>
-      </c>
-      <c r="T42" s="5">
-        <f>SUM(T3:T41)</f>
-        <v/>
-      </c>
-      <c r="U42" s="5">
-        <f>SUM(U3:U41)</f>
-        <v/>
-      </c>
-      <c r="V42" s="5">
-        <f>SUM(V3:V41)</f>
-        <v/>
-      </c>
-      <c r="W42" s="5">
-        <f>SUM(W3:W41)</f>
-        <v/>
-      </c>
-      <c r="X42" s="5">
-        <f>SUM(X3:X41)</f>
-        <v/>
-      </c>
-      <c r="Y42" s="5" t="n"/>
-      <c r="Z42" s="5">
-        <f>SUM(Z3:Z41)</f>
-        <v/>
-      </c>
-      <c r="AA42" s="5">
-        <f>SUM(AA3:AA41)</f>
-        <v/>
-      </c>
-      <c r="AB42" s="5">
-        <f>SUM(AB3:AB41)</f>
-        <v/>
-      </c>
-      <c r="AC42" s="5">
-        <f>SUM(AC3:AC41)</f>
-        <v/>
-      </c>
-      <c r="AD42" s="5">
-        <f>SUM(AD3:AD41)</f>
-        <v/>
-      </c>
-      <c r="AE42" s="5">
-        <f>SUM(AE3:AE41)</f>
-        <v/>
-      </c>
-      <c r="AF42" s="5">
-        <f>SUM(AF3:AF41)</f>
-        <v/>
-      </c>
-      <c r="AG42" s="5">
-        <f>SUM(AG3:AG41)</f>
-        <v/>
-      </c>
-      <c r="AH42" s="5">
-        <f>SUM(AH3:AH41)</f>
-        <v/>
-      </c>
-      <c r="AI42" s="5">
-        <f>SUM(AI3:AI41)</f>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5">
+        <f>SUM(O3:O33)</f>
+        <v/>
+      </c>
+      <c r="P34" s="5">
+        <f>SUM(P3:P33)</f>
+        <v/>
+      </c>
+      <c r="Q34" s="5">
+        <f>SUM(Q3:Q33)</f>
+        <v/>
+      </c>
+      <c r="R34" s="5">
+        <f>SUM(R3:R33)</f>
+        <v/>
+      </c>
+      <c r="S34" s="5">
+        <f>SUM(S3:S33)</f>
+        <v/>
+      </c>
+      <c r="T34" s="5">
+        <f>SUM(T3:T33)</f>
+        <v/>
+      </c>
+      <c r="U34" s="5">
+        <f>SUM(U3:U33)</f>
+        <v/>
+      </c>
+      <c r="V34" s="5">
+        <f>SUM(V3:V33)</f>
+        <v/>
+      </c>
+      <c r="W34" s="5">
+        <f>SUM(W3:W33)</f>
+        <v/>
+      </c>
+      <c r="X34" s="5">
+        <f>SUM(X3:X33)</f>
+        <v/>
+      </c>
+      <c r="Y34" s="5" t="n"/>
+      <c r="Z34" s="5">
+        <f>SUM(Z3:Z33)</f>
+        <v/>
+      </c>
+      <c r="AA34" s="5">
+        <f>SUM(AA3:AA33)</f>
+        <v/>
+      </c>
+      <c r="AB34" s="5">
+        <f>SUM(AB3:AB33)</f>
+        <v/>
+      </c>
+      <c r="AC34" s="5">
+        <f>SUM(AC3:AC33)</f>
+        <v/>
+      </c>
+      <c r="AD34" s="5">
+        <f>SUM(AD3:AD33)</f>
+        <v/>
+      </c>
+      <c r="AE34" s="5">
+        <f>SUM(AE3:AE33)</f>
+        <v/>
+      </c>
+      <c r="AF34" s="5">
+        <f>SUM(AF3:AF33)</f>
+        <v/>
+      </c>
+      <c r="AG34" s="5">
+        <f>SUM(AG3:AG33)</f>
+        <v/>
+      </c>
+      <c r="AH34" s="5">
+        <f>SUM(AH3:AH33)</f>
+        <v/>
+      </c>
+      <c r="AI34" s="5">
+        <f>SUM(AI3:AI33)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AI41"/>
+  <autoFilter ref="A2:AI33"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AI1"/>
   </mergeCells>

--- a/output/bkg pending - PW DEPOT CO., LTD.xlsx
+++ b/output/bkg pending - PW DEPOT CO., LTD.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AG$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$2:$AG$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG52"/>
+  <dimension ref="A1:AG56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -738,8 +738,8 @@
           <t>001</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -865,8 +865,8 @@
           <t>001</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -992,8 +992,8 @@
           <t>001</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1106,25 +1106,25 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260800462</t>
+          <t>HASLS22260800514</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>KXM</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>202609202300</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n"/>
+          <t>202610110000</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -1147,27 +1147,27 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>THAI LOTTE CO., LTD.</t>
+          <t>THAI POLYCARBONATE CO., LTD.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>BISCUITS</t>
+          <t>POLYCARBONATE RESIN , HS CODEIS 3907.40</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>REQUEST CONTAINER GRADE A</t>
+          <t>,PLEASE PROVIDE GOOD AND CLEAN CONTAINER, NO RUST, NO HOLE, NO SMELL WITH STRONG FLOORBOARD (LOAD BY FORKLIFT) AND BULLET SEAL TO THIS SHIPMENT</t>
         </is>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="4" t="n">
         <v>0</v>
@@ -1237,25 +1237,25 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260800514</t>
+          <t>HASLS22260800578</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>KXM</t>
+          <t>PGPO</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>202610110000</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n"/>
+          <t>202609230900</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -1278,27 +1278,27 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>THAI POLYCARBONATE CO., LTD.</t>
+          <t>INOAC (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>POLYCARBONATE RESIN , HS CODEIS 3907.40</t>
+          <t>POLYURETHANE FOAM</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>,PLEASE PROVIDE GOOD AND CLEAN CONTAINER, NO RUST, NO HOLE, NO SMELL WITH STRONG FLOORBOARD (LOAD BY FORKLIFT) AND BULLET SEAL TO THIS SHIPMENT</t>
+          <t>**REQUEST GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="P7" s="4" t="n">
         <v>0</v>
@@ -1368,25 +1368,25 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260800578</t>
+          <t>HASLS22260800853</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>PGPO</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>202609230900</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n"/>
+          <t>202609240200</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1394,32 +1394,33 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx5 </t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>INOAC (THAILAND) CO., LTD.</t>
+          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>POLYURETHANE FOAM</t>
+          <t>REFRIGERATOR</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>**REQUEST GOOD AND CLEAN CONTAINER</t>
+          <t>*No containers with cut and patch marks inside*
+GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
         </is>
       </c>
       <c r="M8" s="4" t="n">
@@ -1429,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P8" s="4" t="n">
         <v>0</v>
@@ -1499,25 +1500,25 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260800857</t>
+          <t>HASLS22260800854</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PGPO</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>202609230900</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n"/>
+          <t>202609240200</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1530,12 +1531,12 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx8 </t>
+          <t xml:space="preserve">40Hx5 </t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1545,7 +1546,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>WASHING MATCHINE</t>
+          <t>REFRIGERATOR</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1561,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P9" s="4" t="n">
         <v>0</v>
@@ -1631,25 +1632,25 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801168</t>
+          <t>HASLS22260800857</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SWBT</t>
+          <t>PGPO</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>202609220700</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n"/>
+          <t>202609230900</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1657,32 +1658,33 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx8 </t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>W.A. RUBBERMATE CO., LTD.</t>
+          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>DISPOSABLE GLOVES</t>
+          <t>WASHING MATCHINE</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>*No containers with cut and patch marks inside*
+GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
         </is>
       </c>
       <c r="M10" s="4" t="n">
@@ -1692,7 +1694,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P10" s="4" t="n">
         <v>0</v>
@@ -1713,7 +1715,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W10" s="4" t="n">
         <v>0</v>
@@ -1777,10 +1779,10 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>202609230100</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n"/>
+          <t>202609231400</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1893,25 +1895,25 @@
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801636</t>
+          <t>HASLS22260801909</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>202609230100</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n"/>
+          <t>202609240200</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1919,36 +1921,36 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>JPIWK</t>
+          <t>JPOSA</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>GLOBAL GREEN CHEMICALS PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t xml:space="preserve">REFINED GLYCERINE 99.5% USP </t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>RQST NO RED WALL CONTAINER,CLEAN CONTAINER NO OIL STAINS , NO RUSTY ,NO CUT OR HOLE</t>
+          <t>Stowage Under Deck Away from Boiler</t>
         </is>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -2024,25 +2026,25 @@
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801908</t>
+          <t>HASLS22260801987</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>KMSU</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>202609230100</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n"/>
+          <t>202609271100</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2050,36 +2052,36 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>JPOSA</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260822</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>GLOBAL GREEN CHEMICALS PUBLIC COMPANY LIMITED</t>
+          <t>TANATEX CHEMICALS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFINED GLYCERINE 99.5% USP </t>
+          <t>CHEMICALS PRODUCT (NON DG)</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>Stowage Under Deck Away from Boiler</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -2155,25 +2157,25 @@
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801978</t>
+          <t>HASLS22260802065</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>KJT</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n"/>
+          <t>202609231400</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2181,32 +2183,32 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>TANATEX CHEMICALS (THAILAND) CO., LTD.</t>
+          <t>ISUZU MOTORS INTERNATIONAL OPERATIONS (THAILAND) COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>CHEMICALS PRODUCT (NON DG)</t>
+          <t>SPARE PARTS</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>REQUEST : CONTAINER MAX GROSS 32.50 TONS</t>
+          <t>RQST GOOD CLEAN AND DRY CONTAINER GRADE 'A'</t>
         </is>
       </c>
       <c r="M14" s="4" t="n">
@@ -2216,7 +2218,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P14" s="4" t="n">
         <v>0</v>
@@ -2286,25 +2288,25 @@
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801983</t>
+          <t>HASLS22260802311</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n"/>
+          <t>202609240200</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2312,42 +2314,42 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>JPMIZ</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>TANATEX CHEMICALS (THAILAND) CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>CHEMICALS PRODUCT (NON DG)</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>*** GOOD &amp; CLEAN CONT.</t>
         </is>
       </c>
       <c r="M15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>0</v>
@@ -2417,25 +2419,25 @@
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801987</t>
+          <t>HASLS22260802314</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>KMSU</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>202609271100</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n"/>
+          <t>202609220400</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2443,36 +2445,36 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>20260822</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>TANATEX CHEMICALS (THAILAND) CO., LTD.</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>CHEMICALS PRODUCT (NON DG)</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -2548,12 +2550,12 @@
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802065</t>
+          <t>HASLS22260802316</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -2563,10 +2565,10 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>202609230100</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n"/>
+          <t>202609220400</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2574,42 +2576,42 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>ISUZU MOTORS INTERNATIONAL OPERATIONS (THAILAND) COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>SPARE PARTS</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>RQST GOOD CLEAN AND DRY CONTAINER GRADE 'A'</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>0</v>
@@ -2679,12 +2681,12 @@
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802308</t>
+          <t>HASLS22260802317</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -2694,10 +2696,10 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>202609281000</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n"/>
+          <t>202609220400</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2705,7 +2707,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -2715,22 +2717,22 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>DOUBLE A (1991) PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>PAPER</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M18" s="4" t="n">
@@ -2810,12 +2812,12 @@
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802309</t>
+          <t>HASLS22260802319</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2825,10 +2827,10 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>202609281000</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n"/>
+          <t>202609220400</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2836,7 +2838,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -2846,22 +2848,22 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260909</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>DOUBLE A (1991) PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>PAPER</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M19" s="4" t="n">
@@ -2941,7 +2943,7 @@
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802314</t>
+          <t>HASLS22260802321</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2956,10 +2958,10 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>202609220200</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n"/>
+          <t>202609220400</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3072,7 +3074,7 @@
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802316</t>
+          <t>HASLS22260802322</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -3087,10 +3089,10 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>202609220200</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n"/>
+          <t>202609220400</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3203,25 +3205,25 @@
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802317</t>
+          <t>HASLS22260802323</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWBT</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>202609220200</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n"/>
+          <t>202609220300</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3229,7 +3231,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -3334,25 +3336,25 @@
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802319</t>
+          <t>HASLS22260802325</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWBT</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>202609220200</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="n"/>
+          <t>202609220300</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3360,7 +3362,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -3465,25 +3467,25 @@
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802321</t>
+          <t>HASLS22260802326</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWBT</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>202609220200</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="n"/>
+          <t>202609220300</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3491,7 +3493,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -3596,25 +3598,25 @@
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802322</t>
+          <t>HASLS22260802387</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>202609220200</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="n"/>
+          <t>202609270600</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3622,22 +3624,22 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx8 </t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -3647,17 +3649,17 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY</t>
         </is>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>0</v>
@@ -3727,12 +3729,12 @@
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802323</t>
+          <t>HASLS22260802608</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>SWBT</t>
+          <t>KUS</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -3742,10 +3744,10 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>202609220700</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="n"/>
+          <t>202609231500</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3753,36 +3755,36 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x8 </t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>DOUBLE A (1991) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>PAPER</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>0</v>
@@ -3858,25 +3860,25 @@
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802325</t>
+          <t>HASLS22260900056</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>SWBT</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>202609220700</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n"/>
+          <t>202609220400</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3884,22 +3886,22 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPFKY</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -3909,38 +3911,38 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>*** FOOD GRADE CONTAINER  ***</t>
         </is>
       </c>
       <c r="M27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="W27" s="4" t="n">
         <v>0</v>
@@ -3989,25 +3991,25 @@
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802326</t>
+          <t>HASLS22260900097</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>SWBT</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>202609220700</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="n"/>
+          <t>202609250500</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -4015,36 +4017,36 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>DOUBLE A (1991) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>PAPER</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0</v>
@@ -4120,25 +4122,25 @@
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802387</t>
+          <t>HASLS22260900173</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>202609271400</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n"/>
+          <t>202609220800</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -4146,32 +4148,32 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx8 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>NALCO INDUSTRIAL SERVICES (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>IMDG SEGREGATION GROUP 1 - ACIDS</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY</t>
+          <t>APPROVAL BY Mr.LEE MINHA DD.07/09/2026 // DG CARGO (CLS 8 / UN 3264)  Request good and clean container</t>
         </is>
       </c>
       <c r="M29" s="4" t="n">
@@ -4181,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P29" s="4" t="n">
         <v>0</v>
@@ -4251,7 +4253,7 @@
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802486</t>
+          <t>HASLS22260900246</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -4266,10 +4268,10 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>202609220200</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n"/>
+          <t>202609220400</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -4277,37 +4279,36 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>JPYOK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>LOGISTICS CARGO EXPRESS CO., LTD.</t>
+          <t>THAI MFC CO., LTD.</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>COOKWARE</t>
+          <t>MELAMINE MOULDING COMPOUND</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>CONTAINER GOOD, CLEAN AND NO SMELL
-HS</t>
+          <t>No damaged and clean container</t>
         </is>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>0</v>
@@ -4334,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W30" s="4" t="n">
         <v>0</v>
@@ -4383,7 +4384,7 @@
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900122</t>
+          <t>HASLS22260900276</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -4401,7 +4402,7 @@
           <t>202609240200</t>
         </is>
       </c>
-      <c r="E31" s="4" t="n"/>
+      <c r="E31" s="4" t="inlineStr"/>
       <c r="F31" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -4409,7 +4410,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>JPTYO</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -4419,22 +4420,22 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>POLYAMIDE RESIN</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>REQUEST GRADE A CONTAIER + SURVEY EMPTY BEFORE PICK UP DD.15/09/26</t>
+          <t>RQST CNTR SOUND AND CLEAN</t>
         </is>
       </c>
       <c r="M31" s="4" t="n">
@@ -4514,7 +4515,7 @@
     <row r="32" ht="13" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900124</t>
+          <t>HASLS22260900436</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -4532,7 +4533,7 @@
           <t>202609240200</t>
         </is>
       </c>
-      <c r="E32" s="4" t="n"/>
+      <c r="E32" s="4" t="inlineStr"/>
       <c r="F32" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -4540,7 +4541,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>JPTYO</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -4550,12 +4551,12 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -4565,7 +4566,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>REQUEST GRADE A CONTAIER + SURVEY EMPTY BEFORE PICK UP DD.15/09/26</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M32" s="4" t="n">
@@ -4645,7 +4646,7 @@
     <row r="33" ht="13" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900125</t>
+          <t>HASLS22260900452</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -4663,7 +4664,7 @@
           <t>202609240200</t>
         </is>
       </c>
-      <c r="E33" s="4" t="n"/>
+      <c r="E33" s="4" t="inlineStr"/>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -4671,12 +4672,12 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>JPTYO</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x4 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -4686,7 +4687,7 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -4696,11 +4697,11 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>REQUEST GRADE A CONTAIER + SURVEY EMPTY BEFORE PICK UP DD.15/09/26</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>0</v>
@@ -4776,25 +4777,25 @@
     <row r="34" ht="13" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900173</t>
+          <t>HASLS22260900453</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n"/>
+          <t>202609240200</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -4802,42 +4803,42 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>NALCO INDUSTRIAL SERVICES (THAILAND) CO., LTD.</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>IMDG SEGREGATION GROUP 1 - ACIDS</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>APPROVAL BY Mr.LEE MINHA DD.07/09/2026 // DG CARGO (CLS 8 / UN 3264)  Request good and clean container</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" s="4" t="n">
         <v>0</v>
@@ -4907,7 +4908,7 @@
     <row r="35" ht="13" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900276</t>
+          <t>HASLS22260900454</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -4925,7 +4926,7 @@
           <t>202609240200</t>
         </is>
       </c>
-      <c r="E35" s="4" t="n"/>
+      <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -4933,7 +4934,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -4943,22 +4944,22 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>POLYAMIDE RESIN</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>RQST CNTR SOUND AND CLEAN</t>
+          <t>1X20' SEABULK1X20' SEABULK</t>
         </is>
       </c>
       <c r="M35" s="4" t="n">
@@ -5038,25 +5039,25 @@
     <row r="36" ht="13" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900284</t>
+          <t>HASLS22260900455</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>202609220200</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n"/>
+          <t>202609240200</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -5064,7 +5065,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>JPHKT</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -5074,12 +5075,12 @@
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -5089,7 +5090,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CTNR</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M36" s="4" t="n">
@@ -5169,25 +5170,25 @@
     <row r="37" ht="13" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900293</t>
+          <t>HASLS22260900457</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>KUS</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>202609231500</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n"/>
+          <t>202609240200</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -5195,12 +5196,12 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>JPTAK</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx5 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -5220,17 +5221,17 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M37" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P37" s="4" t="n">
         <v>0</v>
@@ -5300,25 +5301,25 @@
     <row r="38" ht="13" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900318</t>
+          <t>HASLS22260900484</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>PGPO</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n"/>
+          <t>202609230900</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -5326,42 +5327,43 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>JPMIZ</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">40Hx8 </t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>WASHING MATCHINE</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINERS</t>
+          <t>*No containers with cut and patch marks inside*
+GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>0</v>
@@ -5382,7 +5384,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W38" s="4" t="n">
         <v>0</v>
@@ -5431,7 +5433,7 @@
     <row r="39" ht="13" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900436</t>
+          <t>HASLS22260900601</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -5449,7 +5451,7 @@
           <t>202609240200</t>
         </is>
       </c>
-      <c r="E39" s="4" t="n"/>
+      <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -5457,7 +5459,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -5467,7 +5469,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -5562,25 +5564,25 @@
     <row r="40" ht="13" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900443</t>
+          <t>HASLS22260900836</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>PGPO</t>
+          <t>KUS</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>202609230900</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n"/>
+          <t>202609231500</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -5593,37 +5595,37 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE TIRE MANUFACTURING (THAILAND) CO.,LTD.</t>
+          <t>TROY SIAM CO., LTD.</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>STEEL BOBBINS / PALLET</t>
+          <t xml:space="preserve">HAZARDOUS CHEMICAL </t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>**DO NOT RELEASE CNTR WAIT APPROVE**  MIX DG22GPx1 (CLS 8 / UN 3265)</t>
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P40" s="4" t="n">
         <v>0</v>
@@ -5693,25 +5695,25 @@
     <row r="41" ht="13" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900452</t>
+          <t>HASLS22260901009</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n"/>
+          <t>202609220400</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -5719,7 +5721,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -5729,12 +5731,12 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -5744,7 +5746,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>Good grade or food grade container for WITHOUT PALLET</t>
         </is>
       </c>
       <c r="M41" s="4" t="n">
@@ -5824,25 +5826,25 @@
     <row r="42" ht="13" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900453</t>
+          <t>HASLS22260901012</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n"/>
+          <t>202609220400</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
       <c r="F42" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -5850,7 +5852,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -5860,12 +5862,12 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -5875,7 +5877,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>Good grade or food grade container for WITHOUT PALLET</t>
         </is>
       </c>
       <c r="M42" s="4" t="n">
@@ -5955,25 +5957,25 @@
     <row r="43" ht="13" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900454</t>
+          <t>HASLS22260901014</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="n"/>
+          <t>202609220400</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -5981,7 +5983,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -5991,12 +5993,12 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
@@ -6006,7 +6008,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK1X20' SEABULK</t>
+          <t>Good grade or food grade container for WITHOUT PALLET</t>
         </is>
       </c>
       <c r="M43" s="4" t="n">
@@ -6086,25 +6088,25 @@
     <row r="44" ht="13" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900455</t>
+          <t>HASLS22260901018</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n"/>
+          <t>202609220400</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -6112,7 +6114,7 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -6122,12 +6124,12 @@
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
@@ -6137,7 +6139,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>Good grade or food grade container for WITHOUT PALLET</t>
         </is>
       </c>
       <c r="M44" s="4" t="n">
@@ -6217,25 +6219,25 @@
     <row r="45" ht="13" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900457</t>
+          <t>HASLS22260901293</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWBT</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n"/>
+          <t>202609220300</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -6243,7 +6245,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -6253,22 +6255,22 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>POLYAMIDE RESIN</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>RQST CNTR SOUND &amp; CLEAN</t>
         </is>
       </c>
       <c r="M45" s="4" t="n">
@@ -6348,25 +6350,25 @@
     <row r="46" ht="13" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900484</t>
+          <t>HASLS22260901405</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>PGPO</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>202609230900</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n"/>
+          <t>202609220800</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -6374,43 +6376,42 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx8 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>WASHING MATCHINE</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>*No containers with cut and patch marks inside*
-GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P46" s="4" t="n">
         <v>0</v>
@@ -6478,149 +6479,673 @@
       </c>
     </row>
     <row r="47" ht="13" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="n"/>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5">
-        <f>SUM(M3:M46)</f>
-        <v/>
-      </c>
-      <c r="N47" s="5">
-        <f>SUM(N3:N46)</f>
-        <v/>
-      </c>
-      <c r="O47" s="5">
-        <f>SUM(O3:O46)</f>
-        <v/>
-      </c>
-      <c r="P47" s="5">
-        <f>SUM(P3:P46)</f>
-        <v/>
-      </c>
-      <c r="Q47" s="5">
-        <f>SUM(Q3:Q46)</f>
-        <v/>
-      </c>
-      <c r="R47" s="5">
-        <f>SUM(R3:R46)</f>
-        <v/>
-      </c>
-      <c r="S47" s="5">
-        <f>SUM(S3:S46)</f>
-        <v/>
-      </c>
-      <c r="T47" s="5">
-        <f>SUM(T3:T46)</f>
-        <v/>
-      </c>
-      <c r="U47" s="5">
-        <f>SUM(U3:U46)</f>
-        <v/>
-      </c>
-      <c r="V47" s="5">
-        <f>SUM(V3:V46)</f>
-        <v/>
-      </c>
-      <c r="W47" s="5" t="n"/>
-      <c r="X47" s="5">
-        <f>SUM(X3:X46)</f>
-        <v/>
-      </c>
-      <c r="Y47" s="5">
-        <f>SUM(Y3:Y46)</f>
-        <v/>
-      </c>
-      <c r="Z47" s="5">
-        <f>SUM(Z3:Z46)</f>
-        <v/>
-      </c>
-      <c r="AA47" s="5">
-        <f>SUM(AA3:AA46)</f>
-        <v/>
-      </c>
-      <c r="AB47" s="5">
-        <f>SUM(AB3:AB46)</f>
-        <v/>
-      </c>
-      <c r="AC47" s="5">
-        <f>SUM(AC3:AC46)</f>
-        <v/>
-      </c>
-      <c r="AD47" s="5">
-        <f>SUM(AD3:AD46)</f>
-        <v/>
-      </c>
-      <c r="AE47" s="5">
-        <f>SUM(AE3:AE46)</f>
-        <v/>
-      </c>
-      <c r="AF47" s="5">
-        <f>SUM(AF3:AF46)</f>
-        <v/>
-      </c>
-      <c r="AG47" s="5">
-        <f>SUM(AG3:AG46)</f>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260901406</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>NSSJ</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>2607S</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>202609220800</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY // Upgard 32.5</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="4">
+        <f>SUM(M47:U47)-V47</f>
+        <v/>
+      </c>
+      <c r="Y47" s="4">
+        <f>MAX(0,M47-MAX(0,V47))</f>
+        <v/>
+      </c>
+      <c r="Z47" s="4">
+        <f>MAX(0,N47-MAX(0,V47-SUM(M47:M47)))</f>
+        <v/>
+      </c>
+      <c r="AA47" s="4">
+        <f>MAX(0,O47-MAX(0,V47-SUM(M47:N47)))</f>
+        <v/>
+      </c>
+      <c r="AB47" s="4">
+        <f>MAX(0,P47-MAX(0,V47-SUM(M47:O47)))</f>
+        <v/>
+      </c>
+      <c r="AC47" s="4">
+        <f>MAX(0,Q47-MAX(0,V47-SUM(M47:P47)))</f>
+        <v/>
+      </c>
+      <c r="AD47" s="4">
+        <f>MAX(0,R47-MAX(0,V47-SUM(M47:Q47)))</f>
+        <v/>
+      </c>
+      <c r="AE47" s="4">
+        <f>MAX(0,S47-MAX(0,V47-SUM(M47:R47)))</f>
+        <v/>
+      </c>
+      <c r="AF47" s="4">
+        <f>MAX(0,T47-MAX(0,V47-SUM(M47:S47)))</f>
+        <v/>
+      </c>
+      <c r="AG47" s="4">
+        <f>MAX(0,U47-MAX(0,V47-SUM(M47:T47)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="13" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260901407</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>NSSJ</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>2607S</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>202609220800</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY // Upgard 32.5</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="4">
+        <f>SUM(M48:U48)-V48</f>
+        <v/>
+      </c>
+      <c r="Y48" s="4">
+        <f>MAX(0,M48-MAX(0,V48))</f>
+        <v/>
+      </c>
+      <c r="Z48" s="4">
+        <f>MAX(0,N48-MAX(0,V48-SUM(M48:M48)))</f>
+        <v/>
+      </c>
+      <c r="AA48" s="4">
+        <f>MAX(0,O48-MAX(0,V48-SUM(M48:N48)))</f>
+        <v/>
+      </c>
+      <c r="AB48" s="4">
+        <f>MAX(0,P48-MAX(0,V48-SUM(M48:O48)))</f>
+        <v/>
+      </c>
+      <c r="AC48" s="4">
+        <f>MAX(0,Q48-MAX(0,V48-SUM(M48:P48)))</f>
+        <v/>
+      </c>
+      <c r="AD48" s="4">
+        <f>MAX(0,R48-MAX(0,V48-SUM(M48:Q48)))</f>
+        <v/>
+      </c>
+      <c r="AE48" s="4">
+        <f>MAX(0,S48-MAX(0,V48-SUM(M48:R48)))</f>
+        <v/>
+      </c>
+      <c r="AF48" s="4">
+        <f>MAX(0,T48-MAX(0,V48-SUM(M48:S48)))</f>
+        <v/>
+      </c>
+      <c r="AG48" s="4">
+        <f>MAX(0,U48-MAX(0,V48-SUM(M48:T48)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="13" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260901417</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>KXM</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>202610110000</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>CCL LABEL (THAI) LTD.</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>STICKER LABEL</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="4">
+        <f>SUM(M49:U49)-V49</f>
+        <v/>
+      </c>
+      <c r="Y49" s="4">
+        <f>MAX(0,M49-MAX(0,V49))</f>
+        <v/>
+      </c>
+      <c r="Z49" s="4">
+        <f>MAX(0,N49-MAX(0,V49-SUM(M49:M49)))</f>
+        <v/>
+      </c>
+      <c r="AA49" s="4">
+        <f>MAX(0,O49-MAX(0,V49-SUM(M49:N49)))</f>
+        <v/>
+      </c>
+      <c r="AB49" s="4">
+        <f>MAX(0,P49-MAX(0,V49-SUM(M49:O49)))</f>
+        <v/>
+      </c>
+      <c r="AC49" s="4">
+        <f>MAX(0,Q49-MAX(0,V49-SUM(M49:P49)))</f>
+        <v/>
+      </c>
+      <c r="AD49" s="4">
+        <f>MAX(0,R49-MAX(0,V49-SUM(M49:Q49)))</f>
+        <v/>
+      </c>
+      <c r="AE49" s="4">
+        <f>MAX(0,S49-MAX(0,V49-SUM(M49:R49)))</f>
+        <v/>
+      </c>
+      <c r="AF49" s="4">
+        <f>MAX(0,T49-MAX(0,V49-SUM(M49:S49)))</f>
+        <v/>
+      </c>
+      <c r="AG49" s="4">
+        <f>MAX(0,U49-MAX(0,V49-SUM(M49:T49)))</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="13" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>HASLS22260901435</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>ICVY</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>2607S</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>202609211900</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>UP GRADE 32.5</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="4">
+        <f>SUM(M50:U50)-V50</f>
+        <v/>
+      </c>
+      <c r="Y50" s="4">
+        <f>MAX(0,M50-MAX(0,V50))</f>
+        <v/>
+      </c>
+      <c r="Z50" s="4">
+        <f>MAX(0,N50-MAX(0,V50-SUM(M50:M50)))</f>
+        <v/>
+      </c>
+      <c r="AA50" s="4">
+        <f>MAX(0,O50-MAX(0,V50-SUM(M50:N50)))</f>
+        <v/>
+      </c>
+      <c r="AB50" s="4">
+        <f>MAX(0,P50-MAX(0,V50-SUM(M50:O50)))</f>
+        <v/>
+      </c>
+      <c r="AC50" s="4">
+        <f>MAX(0,Q50-MAX(0,V50-SUM(M50:P50)))</f>
+        <v/>
+      </c>
+      <c r="AD50" s="4">
+        <f>MAX(0,R50-MAX(0,V50-SUM(M50:Q50)))</f>
+        <v/>
+      </c>
+      <c r="AE50" s="4">
+        <f>MAX(0,S50-MAX(0,V50-SUM(M50:R50)))</f>
+        <v/>
+      </c>
+      <c r="AF50" s="4">
+        <f>MAX(0,T50-MAX(0,V50-SUM(M50:S50)))</f>
+        <v/>
+      </c>
+      <c r="AG50" s="4">
+        <f>MAX(0,U50-MAX(0,V50-SUM(M50:T50)))</f>
+        <v/>
       </c>
     </row>
     <row r="51" ht="13" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5">
+        <f>SUM(M3:M50)</f>
+        <v/>
+      </c>
+      <c r="N51" s="5">
+        <f>SUM(N3:N50)</f>
+        <v/>
+      </c>
+      <c r="O51" s="5">
+        <f>SUM(O3:O50)</f>
+        <v/>
+      </c>
+      <c r="P51" s="5">
+        <f>SUM(P3:P50)</f>
+        <v/>
+      </c>
+      <c r="Q51" s="5">
+        <f>SUM(Q3:Q50)</f>
+        <v/>
+      </c>
+      <c r="R51" s="5">
+        <f>SUM(R3:R50)</f>
+        <v/>
+      </c>
+      <c r="S51" s="5">
+        <f>SUM(S3:S50)</f>
+        <v/>
+      </c>
+      <c r="T51" s="5">
+        <f>SUM(T3:T50)</f>
+        <v/>
+      </c>
+      <c r="U51" s="5">
+        <f>SUM(U3:U50)</f>
+        <v/>
+      </c>
+      <c r="V51" s="5">
+        <f>SUM(V3:V50)</f>
+        <v/>
+      </c>
+      <c r="W51" s="5" t="n"/>
+      <c r="X51" s="5">
+        <f>SUM(X3:X50)</f>
+        <v/>
+      </c>
+      <c r="Y51" s="5">
+        <f>SUM(Y3:Y50)</f>
+        <v/>
+      </c>
+      <c r="Z51" s="5">
+        <f>SUM(Z3:Z50)</f>
+        <v/>
+      </c>
+      <c r="AA51" s="5">
+        <f>SUM(AA3:AA50)</f>
+        <v/>
+      </c>
+      <c r="AB51" s="5">
+        <f>SUM(AB3:AB50)</f>
+        <v/>
+      </c>
+      <c r="AC51" s="5">
+        <f>SUM(AC3:AC50)</f>
+        <v/>
+      </c>
+      <c r="AD51" s="5">
+        <f>SUM(AD3:AD50)</f>
+        <v/>
+      </c>
+      <c r="AE51" s="5">
+        <f>SUM(AE3:AE50)</f>
+        <v/>
+      </c>
+      <c r="AF51" s="5">
+        <f>SUM(AF3:AF50)</f>
+        <v/>
+      </c>
+      <c r="AG51" s="5">
+        <f>SUM(AG3:AG50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>PW DEPOT CO., LTD.</t>
         </is>
       </c>
-      <c r="B51" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>78</v>
+      <c r="B55" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>81</v>
       </c>
     </row>
-    <row r="52" ht="13" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="56" ht="13" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="C52" s="5" t="n">
-        <v>78</v>
+      <c r="B56" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AG46"/>
+  <autoFilter ref="A2:AG50"/>
   <mergeCells count="1">
     <mergeCell ref="A1:AG1"/>
   </mergeCells>

--- a/output/bkg pending - PW DEPOT CO., LTD.xlsx
+++ b/output/bkg pending - PW DEPOT CO., LTD.xlsx
@@ -499,15 +499,15 @@
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1">
@@ -600,47 +600,47 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>GP22 Remaining</t>
+          <t>GP22</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>GP42 Remaining</t>
+          <t>GP42</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>GP45 Remaining</t>
+          <t>GP45</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>RE22 Remaining</t>
+          <t>RE22</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>RE45 Remaining</t>
+          <t>RE45</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>UT22 Remaining</t>
+          <t>UT22</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>UT42 Remaining</t>
+          <t>UT42</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>PC22 Remaining</t>
+          <t>PC22</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>PC42 Remaining</t>
+          <t>PC42</t>
         </is>
       </c>
     </row>

--- a/output/bkg pending - PW DEPOT CO., LTD.xlsx
+++ b/output/bkg pending - PW DEPOT CO., LTD.xlsx
@@ -660,8 +660,8 @@
           <t>001</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -741,8 +741,8 @@
           <t>001</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -822,8 +822,8 @@
           <t>001</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -908,7 +908,7 @@
           <t>202610110000</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -990,10 +990,10 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>202609230900</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n"/>
+          <t>202609230830</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1060,233 +1060,232 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>HASLS22260800736</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>KRPTK</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>3AC (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>AIR PURIFIER</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>HASLS22260800853</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>SWMM</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>2609N</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>KRPTK</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx5 </t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>20260916</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>REFRIGERATOR</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>*No containers with cut and patch marks inside*
 GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
         </is>
       </c>
-      <c r="M8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>HASLS22260800854</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>SWMM</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>2609N</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>KRPTK</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx5 </t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>20260916</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>REFRIGERATOR</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>*No containers with cut and patch marks inside*
 GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
         </is>
       </c>
-      <c r="M9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>HASLS22260800857</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>PGPO</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>202609230900</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx8 </t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>20260914</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>WASHING MATCHINE</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>*No containers with cut and patch marks inside*
-GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
-        </is>
-      </c>
       <c r="M10" s="4" t="n">
         <v>0</v>
       </c>
@@ -1294,7 +1293,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P10" s="4" t="n">
         <v>0</v>
@@ -1333,10 +1332,10 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>202609231400</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n"/>
+          <t>202609231200</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1403,25 +1402,25 @@
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801909</t>
+          <t>HASLS22260801827</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>KUS</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n"/>
+          <t>202609240500</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1429,36 +1428,36 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>JPOSA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>GLOBAL GREEN CHEMICALS PUBLIC COMPANY LIMITED</t>
+          <t>THAI SYNTHETIC RUBBERS CO., LTD.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFINED GLYCERINE 99.5% USP </t>
+          <t xml:space="preserve">Polybutadiene Rubber </t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Stowage Under Deck Away from Boiler</t>
+          <t>Good condition; Grade B+</t>
         </is>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1488,25 +1487,25 @@
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260801987</t>
+          <t>HASLS22260801828</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>KMSU</t>
+          <t>KUS</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>202609271100</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n"/>
+          <t>202609240500</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1514,7 +1513,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1524,26 +1523,26 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>20260822</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>TANATEX CHEMICALS (THAILAND) CO., LTD.</t>
+          <t>THAI SYNTHETIC RUBBERS CO., LTD.</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>CHEMICALS PRODUCT (NON DG)</t>
+          <t xml:space="preserve">Polybutadiene Rubber </t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>Good condition; Grade B+</t>
         </is>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1573,25 +1572,25 @@
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802065</t>
+          <t>HASLS22260801909</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>202609231400</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n"/>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1599,42 +1598,42 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>JPOSA</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>ISUZU MOTORS INTERNATIONAL OPERATIONS (THAILAND) COMPANY LIMITED</t>
+          <t>GLOBAL GREEN CHEMICALS PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>SPARE PARTS</t>
+          <t xml:space="preserve">REFINED GLYCERINE 99.5% USP </t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>RQST GOOD CLEAN AND DRY CONTAINER GRADE 'A'</t>
+          <t>Stowage Under Deck Away from Boiler</t>
         </is>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" s="4" t="n">
         <v>0</v>
@@ -1658,25 +1657,25 @@
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802311</t>
+          <t>HASLS22260801987</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>KMSU</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2607S</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n"/>
+          <t>202609271100</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1684,42 +1683,42 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>JPMIZ</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260822</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>TANATEX CHEMICALS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>CHEMICALS PRODUCT (NON DG)</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>*** GOOD &amp; CLEAN CONT.</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="4" t="n">
         <v>0</v>
@@ -1743,25 +1742,25 @@
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802314</t>
+          <t>HASLS22260802247</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWBT</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>202609220400</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n"/>
+          <t>202609220500</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1769,42 +1768,42 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>XTRON AIR-CONDITIONING MANUFACTURE (THAILAND) CO.,LTD</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>AIR CONDITIONER</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>RQS CLEAN &amp; GOOD CONTAINER CONDITION.</t>
         </is>
       </c>
       <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="N16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>0</v>
@@ -1828,25 +1827,25 @@
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802316</t>
+          <t>HASLS22260802311</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>202609220400</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n"/>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1854,22 +1853,22 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>JPMIZ</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1879,17 +1878,17 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>*** GOOD &amp; CLEAN CONT.</t>
         </is>
       </c>
       <c r="M17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="N17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>0</v>
@@ -1913,7 +1912,7 @@
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802317</t>
+          <t>HASLS22260802314</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1928,10 +1927,10 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>202609220400</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n"/>
+          <t>202609220500</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -1998,7 +1997,7 @@
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802319</t>
+          <t>HASLS22260802316</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -2013,10 +2012,10 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>202609220400</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n"/>
+          <t>202609220500</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2083,7 +2082,7 @@
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802321</t>
+          <t>HASLS22260802317</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2098,10 +2097,10 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>202609220400</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n"/>
+          <t>202609220500</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2168,7 +2167,7 @@
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802322</t>
+          <t>HASLS22260802319</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -2183,10 +2182,10 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>202609220400</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n"/>
+          <t>202609220500</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2253,25 +2252,25 @@
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802323</t>
+          <t>HASLS22260802321</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>SWBT</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>202609220300</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n"/>
+          <t>202609220500</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2279,7 +2278,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2338,25 +2337,25 @@
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802325</t>
+          <t>HASLS22260802322</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>SWBT</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>202609220300</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="n"/>
+          <t>202609220500</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2364,7 +2363,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -2423,25 +2422,25 @@
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802326</t>
+          <t>HASLS22260802387</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>SWBT</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>202609220300</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="n"/>
+          <t>202609270600</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2449,22 +2448,22 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx8 </t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>20260909</t>
+          <t>20260911</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -2474,17 +2473,17 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY</t>
         </is>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>0</v>
@@ -2508,12 +2507,12 @@
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260802387</t>
+          <t>HASLS22260802415</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>PGPO</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2523,10 +2522,10 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>202609270600</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="n"/>
+          <t>202609230830</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2534,32 +2533,32 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>RUVVO</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx8 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>20260911</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>YOKOHAMA TIRE MANUFACTURING (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>NEW TIRE</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY</t>
+          <t>RQST CNTR GRADE A</t>
         </is>
       </c>
       <c r="M25" s="4" t="n">
@@ -2569,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>0</v>
@@ -2608,10 +2607,10 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>202609231500</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="n"/>
+          <t>202609240500</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2678,25 +2677,25 @@
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900056</t>
+          <t>HASLS22260900097</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2614N</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>202609220400</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n"/>
+          <t>202609241900</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2704,12 +2703,12 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>JPFKY</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -2719,27 +2718,27 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>DOUBLE A (1991) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>PAPER</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>*** FOOD GRADE CONTAINER  ***</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" s="4" t="n">
         <v>0</v>
@@ -2763,25 +2762,25 @@
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900097</t>
+          <t>HASLS22260900129</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>SKOR</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2614N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>202609250500</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="n"/>
+          <t>202609271030</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2789,36 +2788,36 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>JPTYO</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>DOUBLE A (1991) PUBLIC COMPANY LIMITED</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>PAPER</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQUEST GRADE A CONTAIER + SURVEY EMPTY BEFORE PICK UP DD.19/09/26</t>
         </is>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0</v>
@@ -2848,25 +2847,25 @@
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900173</t>
+          <t>HASLS22260900246</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n"/>
+          <t>202609220500</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2874,42 +2873,42 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260916</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>NALCO INDUSTRIAL SERVICES (THAILAND) CO., LTD.</t>
+          <t>THAI MFC CO., LTD.</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>IMDG SEGREGATION GROUP 1 - ACIDS</t>
+          <t>MELAMINE MOULDING COMPOUND</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>APPROVAL BY Mr.LEE MINHA DD.07/09/2026 // DG CARGO (CLS 8 / UN 3264)  Request good and clean container</t>
+          <t>No damaged and clean container</t>
         </is>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" s="4" t="n">
         <v>0</v>
@@ -2933,25 +2932,25 @@
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900246</t>
+          <t>HASLS22260900436</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>202609220400</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n"/>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -2959,36 +2958,36 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x5 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>THAI MFC CO., LTD.</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>MELAMINE MOULDING COMPOUND</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>No damaged and clean container</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M30" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>0</v>
@@ -3018,7 +3017,7 @@
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900276</t>
+          <t>HASLS22260900452</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -3033,10 +3032,10 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n"/>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
       <c r="F31" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3044,7 +3043,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -3054,22 +3053,22 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>POLYAMIDE RESIN</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>RQST CNTR SOUND AND CLEAN</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M31" s="4" t="n">
@@ -3103,7 +3102,7 @@
     <row r="32" ht="13" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900436</t>
+          <t>HASLS22260900453</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -3118,10 +3117,10 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n"/>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
       <c r="F32" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3129,7 +3128,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -3139,7 +3138,7 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260915</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -3188,7 +3187,7 @@
     <row r="33" ht="13" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900452</t>
+          <t>HASLS22260900454</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -3203,10 +3202,10 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n"/>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3239,7 +3238,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>1X20' SEABULK1X20' SEABULK</t>
         </is>
       </c>
       <c r="M33" s="4" t="n">
@@ -3273,7 +3272,7 @@
     <row r="34" ht="13" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900453</t>
+          <t>HASLS22260900455</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -3288,10 +3287,10 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n"/>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3358,7 +3357,7 @@
     <row r="35" ht="13" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900454</t>
+          <t>HASLS22260900457</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -3373,10 +3372,10 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n"/>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3409,7 +3408,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK1X20' SEABULK</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M35" s="4" t="n">
@@ -3443,25 +3442,25 @@
     <row r="36" ht="13" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900455</t>
+          <t>HASLS22260900502</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n"/>
+          <t>202609291700</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3469,7 +3468,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -3479,12 +3478,12 @@
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>THAI POLYACETAL CO., LTD.</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -3494,7 +3493,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>PLEASE PROVIDE GOOD AND CLEAN CONTAINER, NO RUST, NO HOLE, NO SMELL WITH STRONG FLOORBOARD (LOAD BY FORKLIFT) AND BULLET SEAL TO THIS SHIPMENT</t>
         </is>
       </c>
       <c r="M36" s="4" t="n">
@@ -3528,25 +3527,25 @@
     <row r="37" ht="13" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900457</t>
+          <t>HASLS22260900531</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n"/>
+          <t>202609220500</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3554,42 +3553,42 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>20260915</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>SIRI LABORATORIES CO., LTD.</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t xml:space="preserve">LAUNDRY DETERGENT </t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P37" s="4" t="n">
         <v>0</v>
@@ -3613,25 +3612,21 @@
     <row r="38" ht="13" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900484</t>
+          <t>HASLS22260900550</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>PGPO</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>202609230900</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n"/>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr"/>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3639,43 +3634,42 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx8 </t>
+          <t xml:space="preserve">20'x9 </t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>WASHING MATCHINE</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>*No containers with cut and patch marks inside*
-GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>0</v>
@@ -3699,25 +3693,25 @@
     <row r="39" ht="13" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900601</t>
+          <t>HASLS22260900592</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>KUS</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>202609240200</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n"/>
+          <t>202609240500</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3725,42 +3719,42 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>WANNA ONE TRADING CO.,LTD.</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t xml:space="preserve">LAUNDRY DETERGENT </t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="N39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>0</v>
@@ -3784,25 +3778,25 @@
     <row r="40" ht="13" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260900836</t>
+          <t>HASLS22260900601</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>KUS</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>202609231500</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n"/>
+          <t>202609230600</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3810,7 +3804,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3825,17 +3819,17 @@
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>TROY SIAM CO., LTD.</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAZARDOUS CHEMICAL </t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>**DO NOT RELEASE CNTR WAIT APPROVE**  MIX DG22GPx1 (CLS 8 / UN 3265)</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M40" s="4" t="n">
@@ -3869,12 +3863,12 @@
     <row r="41" ht="13" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260901009</t>
+          <t>HASLS22260900613</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3884,10 +3878,10 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>202609220400</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n"/>
+          <t>202609291700</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3895,7 +3889,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3905,22 +3899,22 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+          <t>THAI SYNTHETIC RUBBERS CO., LTD.</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t xml:space="preserve">Polybutadiene Rubber </t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>Good grade or food grade container for WITHOUT PALLET</t>
+          <t>Good condition; Grade B+</t>
         </is>
       </c>
       <c r="M41" s="4" t="n">
@@ -3954,12 +3948,12 @@
     <row r="42" ht="13" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260901012</t>
+          <t>HASLS22260900614</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -3969,10 +3963,10 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>202609220400</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n"/>
+          <t>202609291700</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
       <c r="F42" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -3980,7 +3974,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3990,22 +3984,22 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+          <t>THAI SYNTHETIC RUBBERS CO., LTD.</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t xml:space="preserve">Polybutadiene Rubber </t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>Good grade or food grade container for WITHOUT PALLET</t>
+          <t>Good condition; Grade B+</t>
         </is>
       </c>
       <c r="M42" s="4" t="n">
@@ -4039,12 +4033,12 @@
     <row r="43" ht="13" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260901014</t>
+          <t>HASLS22260900740</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -4054,10 +4048,10 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>202609220400</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="n"/>
+          <t>202609291700</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -4065,7 +4059,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -4075,22 +4069,22 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+          <t>THAI SYNTHETIC RUBBERS CO., LTD.</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t xml:space="preserve">Polybutadiene Rubber </t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>Good grade or food grade container for WITHOUT PALLET</t>
+          <t>Good condition; Grade B+</t>
         </is>
       </c>
       <c r="M43" s="4" t="n">
@@ -4139,10 +4133,10 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>202609220400</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n"/>
+          <t>202609220500</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -4209,25 +4203,25 @@
     <row r="45" ht="13" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260901293</t>
+          <t>HASLS22260901218</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>SWBT</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>202609220300</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n"/>
+          <t>202609220500</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -4235,42 +4229,42 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>RUVVO</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+          <t>ZHONGCE RUBBER (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>POLYAMIDE RESIN</t>
+          <t>RADIAL TIRES</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>RQST CNTR SOUND &amp; CLEAN</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="N45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="P45" s="4" t="n">
         <v>0</v>
@@ -4294,25 +4288,25 @@
     <row r="46" ht="13" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260901405</t>
+          <t>HASLS22260901293</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>SWBT</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n"/>
+          <t>202609220500</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -4320,7 +4314,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -4335,17 +4329,17 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>POLYAMIDE RESIN</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>RQST CNTR SOUND &amp; CLEAN</t>
         </is>
       </c>
       <c r="M46" s="4" t="n">
@@ -4379,7 +4373,7 @@
     <row r="47" ht="13" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260901406</t>
+          <t>HASLS22260901405</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -4397,7 +4391,7 @@
           <t>202609220800</t>
         </is>
       </c>
-      <c r="E47" s="4" t="n"/>
+      <c r="E47" s="4" t="inlineStr"/>
       <c r="F47" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -4410,7 +4404,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -4430,17 +4424,17 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY // Upgard 32.5</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M47" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>0</v>
@@ -4464,25 +4458,25 @@
     <row r="48" ht="13" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260901407</t>
+          <t>HASLS22260901417</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>KXM</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>202609220800</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="n"/>
+          <t>202610110000</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -4495,27 +4489,27 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>CCL LABEL (THAI) LTD.</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>STICKER LABEL</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY // Upgard 32.5</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M48" s="4" t="n">
@@ -4525,7 +4519,7 @@
         <v>0</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P48" s="4" t="n">
         <v>0</v>
@@ -4549,25 +4543,25 @@
     <row r="49" ht="13" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260901417</t>
+          <t>HASLS22260901503</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>KXM</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>202610110000</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="n"/>
+          <t>202609220500</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
       <c r="F49" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -4575,32 +4569,32 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx5 </t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>CCL LABEL (THAI) LTD.</t>
+          <t>MIDEA REFRIGERATION EQUIPMENT (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>STICKER LABEL</t>
+          <t>AIR CONDITION</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>RQST GOOD CLEAN &amp; DRY CONT.</t>
         </is>
       </c>
       <c r="M49" s="4" t="n">
@@ -4610,7 +4604,7 @@
         <v>0</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P49" s="4" t="n">
         <v>0</v>
@@ -4634,25 +4628,25 @@
     <row r="50" ht="13" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>HASLS22260901435</t>
+          <t>HASLS22260901536</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>ICVY</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2607S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>202609211900</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="n"/>
+          <t>202609220500</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
           <t>THLCH</t>
@@ -4660,32 +4654,32 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>20260916</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>MIDEA REFRIGERATION EQUIPMENT (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>AIR CONDITION</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>UP GRADE 32.5</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M50" s="4" t="n">
@@ -4695,7 +4689,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P50" s="4" t="n">
         <v>0</v>
@@ -4797,7 +4791,7 @@
         <v>48</v>
       </c>
       <c r="C55" s="4" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" ht="13" customHeight="1">
@@ -4810,7 +4804,7 @@
         <v>48</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/output/bkg pending - PW DEPOT CO., LTD.xlsx
+++ b/output/bkg pending - PW DEPOT CO., LTD.xlsx
@@ -487,27 +487,27 @@
   <dimension ref="A1:U56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="18" max="18"/>
+    <col width="5" customWidth="1" min="19" max="19"/>
+    <col width="5" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1">

--- a/output/bkg pending - PW DEPOT CO., LTD.xlsx
+++ b/output/bkg pending - PW DEPOT CO., LTD.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:U86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -607,22 +607,22 @@
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260802359</t>
+          <t>HASLS22260800677</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SWRG</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>202610131130</t>
+          <t>202610090100</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -633,42 +633,43 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>JPTYO</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20261003</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM DEL MONTE CO., LTD.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>SWEET CORN</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CTNR</t>
+          <t>Good and Clean Container (Food Grade)
+(No leaks, no odors, and no oil stains.)</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -692,22 +693,22 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900437</t>
+          <t>HASLS22260800955</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SWVG</t>
+          <t>KUS</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>202610070830</t>
+          <t>202610150400</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -718,22 +719,22 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x6 </t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -743,11 +744,11 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>0</v>
@@ -777,12 +778,12 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900438</t>
+          <t>HASLS22260800966</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SWVG</t>
+          <t>PGPO</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -792,7 +793,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>202610070830</t>
+          <t>202610151900</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -803,22 +804,22 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x10 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20260921</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -828,11 +829,11 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -862,22 +863,22 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900442</t>
+          <t>HASLS22260800970</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SWRG</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>202610131130</t>
+          <t>202610160400</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -888,32 +889,32 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx30 </t>
+          <t xml:space="preserve">40Hx9 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>SHUN YI INTERNATIONAL TRADING CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>PAPER PULP</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>RQST CNTR 32.5 TONS // 40'HQ</t>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
@@ -923,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>0</v>
@@ -947,20 +948,24 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900547</t>
+          <t>HASLS22260801875</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TBN</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>202610090100</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -969,36 +974,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>JPTRG</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x3 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>THAILON TECHNO FIBER LIMITED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>POLYAMIDE 66 TEXTURED YARN</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
@@ -1028,20 +1033,24 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900548</t>
+          <t>HASLS22260802147</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TBN</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>202610130600</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -1050,42 +1059,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>JPTRG</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x11 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>CHIBA METAL (THAILAND) CO.,LTD</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t xml:space="preserve">ELECTRONIC PART/TERMINAL/MICROSPEAKER </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+          <t>good, clean, dry, no leak, no hole</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>0</v>
@@ -1109,20 +1118,24 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900551</t>
+          <t>HASLS22260802337</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TBN</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>202610160400</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -1131,22 +1144,22 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>JPTYO</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x10 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20260926</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1156,17 +1169,17 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>0</v>
@@ -1190,22 +1203,22 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900800</t>
+          <t>HASLS22260802338</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>202610080830</t>
+          <t>202610160400</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -1216,22 +1229,22 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPTYO</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1241,17 +1254,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P9" s="2" t="n">
         <v>0</v>
@@ -1275,12 +1288,12 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900802</t>
+          <t>HASLS22260802359</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWRG</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1290,7 +1303,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>202610080830</t>
+          <t>202610141700</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1301,12 +1314,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1316,7 +1329,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1326,17 +1339,17 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>0</v>
@@ -1360,7 +1373,7 @@
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900808</t>
+          <t>HASLS22260900120</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1375,7 +1388,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>202610080830</t>
+          <t>202610071530</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -1386,42 +1399,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>3AC (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>AIR PURIFIER</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>0</v>
@@ -1445,12 +1458,12 @@
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900809</t>
+          <t>HASLS22260900442</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWRG</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1460,7 +1473,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>202610080830</t>
+          <t>202610141700</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1471,42 +1484,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx30 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>SHUN YI INTERNATIONAL TRADING CO., LTD.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>PAPER PULP</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>RQST CNTR 32.5 TONS // 40'HQ</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>0</v>
@@ -1530,24 +1543,20 @@
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901258</t>
+          <t>HASLS22260900547</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>202610090100</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1556,22 +1565,22 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPTRG</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x3 </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1581,11 +1590,11 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1615,24 +1624,20 @@
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901276</t>
+          <t>HASLS22260900548</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SWVG</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>202610070830</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1641,36 +1646,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>JPTRG</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x11 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20260925</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>SHIN-ETSU SILICONES (THAILAND) LTD.</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>SILICONE</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Container : Good , Clean, No smell container are requested.</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
@@ -1700,24 +1705,20 @@
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901417</t>
+          <t>HASLS22260900551</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>KXM</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>202610101500</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1726,42 +1727,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x10 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260926</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>CCL LABEL (THAI) LTD.</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>STICKER LABEL</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>REQ GOOD AND CLEAN CONTAINER</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="2" t="n">
         <v>0</v>
@@ -1785,22 +1786,22 @@
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901483</t>
+          <t>HASLS22260901216</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWSR</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>202610070300</t>
+          <t>202610130600</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1811,42 +1812,42 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNXMN</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">20'x4 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>SS EXCELLENT NETWORK CO.,LTD</t>
+          <t>THAI POLYCARBONATE CO., LTD.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>COPPER INGOT</t>
+          <t>POLYCARBONATE RESIN (HS CODE. 3907.40)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>RQST CONTAINER 32.5 TONS.</t>
+          <t>Loading with pallet-by forklift, required good container with strong floorboard and bullet seal to this shipment***</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P16" s="2" t="n">
         <v>0</v>
@@ -1870,22 +1871,22 @@
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901484</t>
+          <t>HASLS22260901251</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWRG</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>202610090100</t>
+          <t>202610141700</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1896,36 +1897,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x5 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20260926</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>SS EXCELLENT NETWORK CO.,LTD</t>
+          <t>THAI SYNTHETIC RUBBERS CO., LTD.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>COPPER INGOT</t>
+          <t xml:space="preserve">Polybutadiene Rubber </t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>RQST CONTAINER 30 TONS</t>
+          <t>RQST Good condition; Grade B+</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1955,22 +1956,22 @@
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901485</t>
+          <t>HASLS22260901417</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>KXM</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202610090100</t>
+          <t>202610101500</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1981,32 +1982,32 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx5 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20260926</t>
+          <t>20260910</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>SS EXCELLENT NETWORK CO.,LTD</t>
+          <t>CCL LABEL (THAI) LTD.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>COPPER INGOT</t>
+          <t>STICKER LABEL</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>RQST CONTAINER 32.5 TONS.</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
@@ -2016,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P18" s="2" t="n">
         <v>0</v>
@@ -2040,22 +2041,22 @@
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901519</t>
+          <t>HASLS22260901455</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SWRG</t>
+          <t>PCCP</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>202610131130</t>
+          <t>202610121600</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -2066,42 +2067,42 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>JPKIJ</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>THAI SYNTHETIC RUBBERS CO., LTD.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t xml:space="preserve">Polybutadiene Rubber </t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+          <t>RQST GOOD CONDITION : GRADE B+</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" s="2" t="n">
         <v>0</v>
@@ -2125,22 +2126,22 @@
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901713</t>
+          <t>HASLS22260901485</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>202610080830</t>
+          <t>202610090100</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -2151,42 +2152,42 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx5 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20260928</t>
+          <t>20260926</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>SS EXCELLENT NETWORK CO.,LTD</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>COPPER INGOT</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>RQST CONTAINER 32.5 TONS.</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>0</v>
@@ -2210,22 +2211,22 @@
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901910</t>
+          <t>HASLS22260901522</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SWVG</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>202610070830</t>
+          <t>202610200800</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -2236,7 +2237,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>JPKIJ</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2246,22 +2247,22 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>SHIN-ETSU SILICONES (THAILAND) LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>SILICONE</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Good , Clean, No smell container are requested.</t>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
@@ -2295,12 +2296,12 @@
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901989</t>
+          <t>HASLS22260901524</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2310,7 +2311,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>202610192200</t>
+          <t>202610200800</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -2321,17 +2322,17 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPTAK</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x13 </t>
+          <t xml:space="preserve">20'x3 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2346,11 +2347,11 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>REQUEST SEA BULK CONTAIER + SURVEY EMPTY BEFORE PICK UP (REQ SURVEY 30/09/2026)</t>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -2380,22 +2381,22 @@
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902139</t>
+          <t>HASLS22260901660</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>PCCP</t>
+          <t>KXM</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>202610121600</t>
+          <t>202611080430</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -2406,42 +2407,45 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20260926</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>SRI TRANG GLOVES (THAILAND) PUBLIC COMPANY LIMITED</t>
+          <t>OATSIDE (THAILAND) LIMITED.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>LATEX GLOVES</t>
+          <t>OAT MILK ( GOOD GRADE CONTAINER REQUIRED)</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>REQ GOOD AND CLEAN CONTAINER</t>
+          <t>Good dry and clean container
+Food grade container only
+Rust-Free interior
+No Physical Damage.</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P23" s="2" t="n">
         <v>0</v>
@@ -2465,12 +2469,12 @@
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902245</t>
+          <t>HASLS22260901713</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SWRG</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2480,7 +2484,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>202610131130</t>
+          <t>202610071530</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -2491,22 +2495,22 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>JPKIJ</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260928</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2516,17 +2520,17 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CTNR</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" s="2" t="n">
         <v>0</v>
@@ -2550,22 +2554,22 @@
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902292</t>
+          <t>HASLS22260901767</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>202610070300</t>
+          <t>202610071530</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -2576,32 +2580,32 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>CNXMN</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261003</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>NATURAL RUBBER THREAD CO., LTD.</t>
+          <t>BARBE (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>RUBBER THREAD</t>
+          <t>RUBBER COMPOUND</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>RQST CONTAINER 32.5 TONS. // GOOD CLEAN NO SMELL CONTAINER</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
@@ -2611,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P25" s="2" t="n">
         <v>0</v>
@@ -2635,22 +2639,22 @@
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902464</t>
+          <t>HASLS22260901779</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>PCCP</t>
+          <t>SWVG</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>202610121600</t>
+          <t>202610070930</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -2661,36 +2665,36 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>JPIYM</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x5 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261003</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>GANG YAN DIAMOND TOOLS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>SAW BLADE</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINERS</t>
+          <t>Special Remark : Request well clean and dry cntrs</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2720,22 +2724,22 @@
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902465</t>
+          <t>HASLS22260901825</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>PCCP</t>
+          <t>KXM</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>202610121600</t>
+          <t>202610101500</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -2746,42 +2750,42 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>JPHKT</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>APEX CIRCUIT (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>PRINTED CIRCUIT BOARD NO BRAND</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINERS</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" s="2" t="n">
         <v>0</v>
@@ -2805,22 +2809,22 @@
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902542</t>
+          <t>HASLS22260901872</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SWDN</t>
+          <t>SWBT</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2616N</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>202610070300</t>
+          <t>202610160100</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -2831,42 +2835,43 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx7 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20261001</t>
+          <t>20261002</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>ALLIANCE LAUNDRY (THAILAND) CO., LTD.</t>
+          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>SELF SERVICE WASHERS AND TUMBLE DRYERS</t>
+          <t>REFRIGERATOR</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>REQ GOOD AND CLEAN CONTAINER</t>
+          <t>*No containers with cut and patch marks inside*
+GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P28" s="2" t="n">
         <v>0</v>
@@ -2890,22 +2895,22 @@
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902549</t>
+          <t>HASLS22260901911</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWRG</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>202610300100</t>
+          <t>202610141700</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -2916,42 +2921,42 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20260926</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>THAIXING CIRCUITS CO., LTD.</t>
+          <t>SHIN-ETSU SILICONES (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>MULTILAYER PRINTED CIRCUIT BOARD</t>
+          <t>SILICONE</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>Good , Clean, No smell container are requested.</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" s="2" t="n">
         <v>0</v>
@@ -2975,12 +2980,12 @@
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902725</t>
+          <t>HASLS22260901913</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>SWRG</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2990,7 +2995,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>202610192200</t>
+          <t>202610141700</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -3001,7 +3006,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3011,22 +3016,22 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>PACIFIC SUGAR CORPORATION LIMITED</t>
+          <t>SHIN-ETSU SILICONES (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>SILICONE</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD AND CLEAN CONTAINER FOR FOOD</t>
+          <t>Good , Clean, No smell container are requested.</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
@@ -3060,7 +3065,7 @@
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902799</t>
+          <t>HASLS22260901989</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -3075,7 +3080,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>202610192200</t>
+          <t>202610200800</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -3086,161 +3091,4319 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
+          <t>JPNGO</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x13 </t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST SEA BULK CONTAIER + SURVEY EMPTY BEFORE PICK UP (REQ SURVEY 30/09/2026)</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901995</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>202610071530</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
           <t>VNSGN</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>20260902</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>LINNBAO MUYE CO.,LTD</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>RUBBER WOOD</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>RQST CNTR 32.5 TONS // 40'HQ</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="13" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="3" t="n"/>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n"/>
-      <c r="M32" s="3">
-        <f>SUM(M2:M31)</f>
-        <v/>
-      </c>
-      <c r="N32" s="3">
-        <f>SUM(N2:N31)</f>
-        <v/>
-      </c>
-      <c r="O32" s="3">
-        <f>SUM(O2:O31)</f>
-        <v/>
-      </c>
-      <c r="P32" s="3">
-        <f>SUM(P2:P31)</f>
-        <v/>
-      </c>
-      <c r="Q32" s="3">
-        <f>SUM(Q2:Q31)</f>
-        <v/>
-      </c>
-      <c r="R32" s="3">
-        <f>SUM(R2:R31)</f>
-        <v/>
-      </c>
-      <c r="S32" s="3">
-        <f>SUM(S2:S31)</f>
-        <v/>
-      </c>
-      <c r="T32" s="3">
-        <f>SUM(T2:T31)</f>
-        <v/>
-      </c>
-      <c r="U32" s="3">
-        <f>SUM(U2:U31)</f>
-        <v/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>TROY SIAM CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HAZARDOUS CHEMICAL </t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>**APPROVE DG IN SYSTEM**DG22GPx1 (CLS 8 / UN 3267)</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902024</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>PCCP</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>202610121600</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>JPNGO</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>1X20' SEABULK</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902025</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>PCCP</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>202610121600</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>JPNGO</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>1X20' SEABULK</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35" ht="13" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>PCCP</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>202610121600</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>JPNGO</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>1X20' SEABULK</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36" ht="13" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>HASLS22260902027</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>202610160400</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>JPYKK</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>1X20' SEABULK</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902028</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>202610160400</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>JPYKK</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>1X20' SEABULK</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="13" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902029</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>202610160400</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>JPYKK</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>1X20' SEABULK</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="13" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902030</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>202610160400</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>JPYKK</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>1X20' SEABULK</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="13" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902048</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>202610160400</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="13" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902063</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SWRG</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>202610141700</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>JPMOJ</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x5 </t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>RESIN-PALLET,NO RED WALL CONTAINER,CLEAN CONTAINER NO OIL STAINS , NO RUSTY ,NO CUT OR HOLE</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="13" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902071</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>202610160400</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>IRPC PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="13" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902153</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>TBN</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>JPYKK</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x10 </t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="13" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902206</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>PCCP</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>202610121600</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRI ETHANOLAMINE </t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902217</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SWVG</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>202610070930</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x2 </t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>SHIN-ETSU SILICONES (THAILAND) LTD.</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>SILICONE</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Good , Clean, No smell container</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="13" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902220</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>KMTP</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>202610142200</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>DELTA DAIKI METAL (THAILAND) CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>MIXED METAL</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>RQST UPGRADE CNTR 30 TONS</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="13" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902243</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SWVG</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>202610070930</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>MITSUBISHI ELECTRIC SIAM COMPRESSOR INDUSTRY CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>SCROLL COMPRESSOR FOR AIR CONDITIONER</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="13" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902245</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SWRG</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>202610141700</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>JPKIJ</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="13" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902255</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>202610071530</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx5 </t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>HMC POLYMERS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>POLYPROPYLENE</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="13" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902295</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>HMVY</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>202610200800</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>EURO-ORIENTAL TRADING CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>HEVEAGRAFT 5050 LATEX</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>** APPROVED BY KIM JAE-HYUNG DD.24/09/2026 ** *FLEXIBAG ONDECK*
+Survey : 2026-10-02</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="13" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902297</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>KUS</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>2616N</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>202610150400</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x6 </t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902298</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>KUS</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>2616N</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>202610150400</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902302</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>202610160400</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x2 </t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902303</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>202610160400</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x3 </t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902304</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SWIC</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>202610160400</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="13" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902328</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>TBN</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>JPYKK</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x5 </t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="13" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902351</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SWVG</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>202610070930</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>RUVVO</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>YOKOHAMA TIRE MANUFACTURING (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>NEW TIRE</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>RQST CNTR GRADE A</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="13" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902358</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SWRG</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>202610141700</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx8 </t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" ht="13" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902370</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SWSR</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>202610130600</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x2 </t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>DOUBLE A (1991) PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" ht="13" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902390</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SWRG</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>202610141700</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>JPKIJ</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x2 </t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>IRPC PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" ht="13" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902432</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>KXM</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>202610101500</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POLYAMIDE RESIN </t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Sound and Clean</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" ht="13" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902438</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>202610071530</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>JPTOS</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x6 </t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>DELTA DAIKI METAL (THAILAND) CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>ALUMINUM</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" ht="13" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902440</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>KXM</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>202610101500</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POLYAMIDE RESIN </t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Sound and Clean</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" ht="13" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902445</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>KXM</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>202610101500</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POLYAMIDE RESIN </t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Sound and Clean</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="13" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902446</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>KXM</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>202610101500</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POLYAMIDE RESIN </t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Sound and Clean</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" ht="13" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902450</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>KXM</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>202610101500</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>IDJKT</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x2 </t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POLYAMIDE RESIN </t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Sound and Clean</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" ht="13" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902511</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>202610071530</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>GOODSCOUR INDUSTRIAL CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>HOUSEHOLD PRODUCTS SCOURING PAD (POLYESTER)</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" ht="13" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902549</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>202610300100</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>20260926</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>THAIXING CIRCUITS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>MULTILAYER PRINTED CIRCUIT BOARD</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" ht="13" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902569</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>202610071530</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>JOYSON-TOA SAFETY SYSTEMS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>MAGNESIUM SCRAP</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" ht="13" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902621</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SWSP</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>202610071530</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx6 </t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>MIDEA INTELLIGENT MANUFACTURING (THAILAND) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>REFRIGERATOR</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" ht="13" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902629</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>KUS</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>2616N</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>202610150400</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" ht="13" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902669</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>HMVY</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>202610200800</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>JPNGO</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x6 </t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST SEA BULK CONTAIER + SURVEY DD.19/09/2026 EMPTY BEFORE PICK UP</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" ht="13" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902707</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>DJCF</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>0152N</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>202610112300</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>REQ. RESIN-NON PALLET,CLEAN CONTAINER NO OIL STAINS</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" ht="13" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902725</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SWAL</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>202610200800</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>PACIFIC SUGAR CORPORATION LIMITED</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Sugar</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>REQUEST GOOD AND CLEAN CONTAINER FOR FOOD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" ht="13" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902741</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SWRG</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>202610141700</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx8 </t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" ht="13" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902816</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>KUS</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>2616N</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>202610150400</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x8 </t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" ht="13" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902818</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>PGPO</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>202610151900</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x6 </t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" ht="13" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902819</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>PGPO</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>202610151900</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x4 </t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" ht="13" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000076</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>202610090100</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>TWKEL</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>20261003</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CTNR</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" ht="13" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000190</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>202610090100</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>HKHKG</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>SS EXCELLENT NETWORK CO.,LTD</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>COPPER INGOT</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>RQST CONTAINER 30 TONS</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" ht="13" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n"/>
+      <c r="C81" s="3" t="n"/>
+      <c r="D81" s="3" t="n"/>
+      <c r="E81" s="3" t="n"/>
+      <c r="F81" s="3" t="n"/>
+      <c r="G81" s="3" t="n"/>
+      <c r="H81" s="3" t="n"/>
+      <c r="I81" s="3" t="n"/>
+      <c r="J81" s="3" t="n"/>
+      <c r="K81" s="3" t="n"/>
+      <c r="L81" s="3" t="n"/>
+      <c r="M81" s="3">
+        <f>SUM(M2:M80)</f>
+        <v/>
+      </c>
+      <c r="N81" s="3">
+        <f>SUM(N2:N80)</f>
+        <v/>
+      </c>
+      <c r="O81" s="3">
+        <f>SUM(O2:O80)</f>
+        <v/>
+      </c>
+      <c r="P81" s="3">
+        <f>SUM(P2:P80)</f>
+        <v/>
+      </c>
+      <c r="Q81" s="3">
+        <f>SUM(Q2:Q80)</f>
+        <v/>
+      </c>
+      <c r="R81" s="3">
+        <f>SUM(R2:R80)</f>
+        <v/>
+      </c>
+      <c r="S81" s="3">
+        <f>SUM(S2:S80)</f>
+        <v/>
+      </c>
+      <c r="T81" s="3">
+        <f>SUM(T2:T80)</f>
+        <v/>
+      </c>
+      <c r="U81" s="3">
+        <f>SUM(U2:U80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="13" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="13" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
           <t>PW DEPOT CO., LTD.</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="37" ht="13" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="B85" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="86" ht="13" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>112</v>
+      <c r="B86" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U31"/>
+  <autoFilter ref="A1:U80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - PW DEPOT CO., LTD.xlsx
+++ b/output/bkg pending - PW DEPOT CO., LTD.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092D050"/>
       </patternFill>
     </fill>
     <fill>
@@ -92,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -100,10 +105,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -471,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U57"/>
+  <dimension ref="A1:U56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -481,7 +489,7 @@
     <col width="4" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
@@ -607,20 +615,24 @@
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801848</t>
+          <t>HASLS22260801507</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>TBN</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>202610240200</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -629,42 +641,43 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x3 </t>
+          <t xml:space="preserve">40Hx7 </t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>DISH WASHER</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+          <t>*No containers with cut and patch marks inside*
+GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -688,24 +701,20 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900176</t>
+          <t>HASLS22260801848</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>202610220200</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -714,22 +723,22 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>JPTYO</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x3 </t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -739,11 +748,11 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GRADE A CONTAIER + SURVEY EMPTY BEFORE PICK UP DD.15/09/26</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>0</v>
@@ -773,22 +782,22 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900390</t>
+          <t>HASLS22260900167</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>202610201800</t>
+          <t>202610240200</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -799,36 +808,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPTRG</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x32 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>LONGWELL COMPANY (THAILAND) CO.,LTD.</t>
+          <t>GC-M PTA COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>POWER CORD</t>
+          <t>PURIFIED TEREPHTHALIC ACID (HS CODE: 291736)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>SPECIAL REQUEST : SEABULK CONTAINER (FOR TOYOBO SHIPMENT)</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -858,20 +867,24 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900547</t>
+          <t>HASLS22260900170</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TBN</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr"/>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>202610252330</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -885,31 +898,31 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x3 </t>
+          <t xml:space="preserve">20'x32 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>GC-M PTA COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>PURIFIED TEREPHTHALIC ACID (HS CODE: 291736)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+          <t>SPECIAL REQUEST : SEABULK CONTAINER (FOR TOYOBO SHIPMENT)</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -939,20 +952,24 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900548</t>
+          <t>HASLS22260900175</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TBN</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>202610280600</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -961,22 +978,22 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>JPTRG</t>
+          <t>JPTYO</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x11 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -986,11 +1003,11 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+          <t>REQUEST GRADE A CONTAIER + SURVEY EMPTY BEFORE PICK UP DD.15/09/26</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
@@ -1020,7 +1037,7 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900551</t>
+          <t>HASLS22260900547</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1042,17 +1059,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>JPTRG</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x10 </t>
+          <t xml:space="preserve">20'x3 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20260926</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1071,7 +1088,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1101,24 +1118,20 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900880</t>
+          <t>HASLS22260900548</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>202610152200</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -1127,37 +1140,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>KRUSN</t>
+          <t>JPTRG</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">20'x11 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20260925</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>UNITEX RUBBER CO.,LTD</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>NATURAL RUBBER LATEX</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>**APPROVED BY MJ CHANG DD.30/09/26** *FLEXIBAG ONDECK*
-Survey : 2026-10-06, Pickup : 2026-10-07 GOOD AND CLEAN CONTAINER</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>0</v>
@@ -1187,24 +1199,20 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901417</t>
+          <t>HASLS22260900551</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2608S</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>202610210800</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1213,42 +1221,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">20'x10 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20260910</t>
+          <t>20260926</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>CCL LABEL (THAI) LTD.</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>STICKER LABEL</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" s="2" t="n">
         <v>0</v>
@@ -1272,22 +1280,22 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901462</t>
+          <t>HASLS22260901417</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SWBT</t>
+          <t>YSVY</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2616N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>202610161300</t>
+          <t>202610220430</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1298,27 +1306,27 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20260919</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>TPV TECHNOLOGY (THAILAND) CO., LTD.</t>
+          <t>CCL LABEL (THAI) LTD.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>MONITOR SCREEN</t>
+          <t>STICKER LABEL</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1333,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>0</v>
@@ -1357,22 +1365,22 @@
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901496</t>
+          <t>HASLS22260901660</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>KXM</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>202610220200</t>
+          <t>202611090200</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -1383,115 +1391,30 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x7 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>OATSIDE (THAILAND) LIMITED.</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>OAT MILK ( GOOD GRADE CONTAINER REQUIRED)</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>REQUEST SEA BULK CONTAIER + SURVEY DD.19/09/2026 EMPTY BEFORE PICK UP</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901660</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>KXM</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>202611090200</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx3 </t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>20261005</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>OATSIDE (THAILAND) LIMITED.</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>OAT MILK ( GOOD GRADE CONTAINER REQUIRED)</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Good dry and clean container
 Food grade container only
@@ -1499,14 +1422,99 @@
 No Physical Damage.</t>
         </is>
       </c>
+      <c r="M11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901703</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>202610240200</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x11 </t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>0</v>
@@ -1530,22 +1538,22 @@
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901682</t>
+          <t>HASLS22260901774</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>202610220200</t>
+          <t>202610240700</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1556,32 +1564,32 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>JPMYJ</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>ELNA (THAILAND) CO.,LTD.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>ELECTROLYTIC CONDENSER SOLUTION</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CTNR</t>
+          <t>**REQ GOOD, CLEAN, NO LEAK AND GRADE A CONTAINER</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
@@ -1591,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>0</v>
@@ -1615,22 +1623,22 @@
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901683</t>
+          <t>HASLS22260902027</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>202610220200</t>
+          <t>202610170200</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1641,22 +1649,22 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>JPMYJ</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1666,17 +1674,17 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CTNR</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>0</v>
@@ -1700,22 +1708,22 @@
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901703</t>
+          <t>HASLS22260902028</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>202610221200</t>
+          <t>202610170200</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1726,22 +1734,22 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx9 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1751,17 +1759,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P15" s="2" t="n">
         <v>0</v>
@@ -1785,22 +1793,22 @@
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901902</t>
+          <t>HASLS22260902029</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>202610220200</t>
+          <t>202610170200</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1811,22 +1819,22 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx8 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1836,17 +1844,17 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CTNR</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P16" s="2" t="n">
         <v>0</v>
@@ -1870,22 +1878,22 @@
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901989</t>
+          <t>HASLS22260902030</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>202610201800</t>
+          <t>202610170200</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1896,22 +1904,22 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>JPUKB</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x7 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1921,11 +1929,11 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>REQUEST SEA BULK CONTAIER + SURVEY EMPTY BEFORE PICK UP (REQ SURVEY 30/09/2026)</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1955,22 +1963,22 @@
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902027</t>
+          <t>HASLS22260902236</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202610152200</t>
+          <t>202610252330</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1981,7 +1989,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1991,22 +1999,22 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261010</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>POLYAMIDE RESIN</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>Sound and Clean</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
@@ -2040,22 +2048,22 @@
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902028</t>
+          <t>HASLS22260902238</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>202610152200</t>
+          <t>202610252330</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -2066,7 +2074,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2076,22 +2084,22 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261010</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>POLYAMIDE RESIN</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>Sound and Clean</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
@@ -2125,12 +2133,12 @@
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902029</t>
+          <t>HASLS22260902366</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2140,7 +2148,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>202610152200</t>
+          <t>202610240900</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -2151,22 +2159,22 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x7 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2176,11 +2184,11 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -2210,22 +2218,22 @@
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902030</t>
+          <t>HASLS22260902385</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>202610152200</t>
+          <t>202610240200</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -2236,42 +2244,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx6 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>BERLI JUCKER CELLOX LIMITED</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>TISSUE</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>REQUEST GOOD GRADE CONTAINER</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P21" s="2" t="n">
         <v>0</v>
@@ -2295,22 +2303,22 @@
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902037</t>
+          <t>HASLS22260902435</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>202610220200</t>
+          <t>202610251100</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -2321,7 +2329,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2331,22 +2339,22 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>DOUBLE A (1991) PUBLIC COMPANY LIMITED</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>PAPER</t>
+          <t xml:space="preserve">POLYAMIDE RESIN </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>Sound and Clean</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
@@ -2380,22 +2388,22 @@
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902071</t>
+          <t>HASLS22260902451</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>NSSJ</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2608S</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>202610152200</t>
+          <t>202610251100</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -2406,42 +2414,42 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>IRPC PUBLIC COMPANY LIMITED</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t xml:space="preserve">POLYAMIDE RESIN </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>Sound and Clean</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P23" s="2" t="n">
         <v>0</v>
@@ -2465,22 +2473,22 @@
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902102</t>
+          <t>HASLS22260902492</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>202610191200</t>
+          <t>202610252330</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -2491,12 +2499,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x6 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2506,7 +2514,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>THAI POLYACETAL CO., LTD.</t>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2516,11 +2524,11 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>PLEASE PROVIDE GOOD AND CLEAN CONTAINER, NO RUST, NO HOLE, NO SMELL WITH STRONG FLOORBOARD (LOAD BY FORKLIFT) AND BULLET SEAL TO THIS SHIPMENT</t>
+          <t>REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
@@ -2550,22 +2558,22 @@
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902110</t>
+          <t>HASLS22260902549</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>202610201800</t>
+          <t>202611021800</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -2576,42 +2584,42 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20260926</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>THAIXING CIRCUITS CO., LTD.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>MULTILAYER PRINTED CIRCUIT BOARD</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" s="2" t="n">
         <v>0</v>
@@ -2635,22 +2643,22 @@
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902162</t>
+          <t>HASLS22260902590</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>202610221200</t>
+          <t>202610250800</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -2661,42 +2669,42 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">20'x8 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>SRI TRANG AGRO-INDUSTRY PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>NATURAL RUBBER STR20</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>REQ. RESIN-PALLET,CLEAN CONTAINER NO OIL STAINS</t>
+          <t>Grade B container with Strong wooden floor for heavy cargo and without wood splinter,Use Forklift to stuffing the cargo into the container</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P26" s="2" t="n">
         <v>0</v>
@@ -2720,22 +2728,22 @@
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902301</t>
+          <t>HASLS22260902595</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>202610221200</t>
+          <t>202610250800</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -2746,22 +2754,22 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPMYJ</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2771,7 +2779,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>*** GOOD &amp; CLEAN CONT. &amp; GRADE A ***</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
@@ -2781,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P27" s="2" t="n">
         <v>0</v>
@@ -2805,7 +2813,7 @@
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902394</t>
+          <t>HASLS22260902625</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2820,7 +2828,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>202610201800</t>
+          <t>202610220200</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -2831,7 +2839,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2841,12 +2849,12 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2856,7 +2864,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
@@ -2890,12 +2898,12 @@
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902492</t>
+          <t>HASLS22260902626</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>SWAL</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2916,22 +2924,22 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x6 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2941,11 +2949,11 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N29" s="2" t="n">
         <v>0</v>
@@ -2975,7 +2983,7 @@
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902543</t>
+          <t>HASLS22260902627</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2990,7 +2998,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>202610201800</t>
+          <t>202610220200</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -3001,22 +3009,22 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -3026,17 +3034,17 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>REQ. RESIN-PALLET,CLEAN CONTAINER NO OIL STAINS</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30" s="2" t="n">
         <v>0</v>
@@ -3060,7 +3068,7 @@
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902544</t>
+          <t>HASLS22260902630</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -3075,7 +3083,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>202610201800</t>
+          <t>202610220200</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -3086,22 +3094,22 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -3111,17 +3119,17 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>REQ. RESIN-PALLET,CLEAN CONTAINER NO OIL STAINS</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P31" s="2" t="n">
         <v>0</v>
@@ -3145,22 +3153,22 @@
     <row r="32" ht="13" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902549</t>
+          <t>HASLS22260902631</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWAL</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>202611012100</t>
+          <t>202610220200</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -3171,42 +3179,42 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20260926</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>THAIXING CIRCUITS CO., LTD.</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>MULTILAYER PRINTED CIRCUIT BOARD</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="2" t="n">
         <v>0</v>
@@ -3230,12 +3238,12 @@
     <row r="33" ht="13" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902669</t>
+          <t>HASLS22260902632</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>SWAL</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3256,22 +3264,22 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x6 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -3281,11 +3289,11 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>REQUEST SEA BULK CONTAIER + SURVEY DD.19/09/2026 EMPTY BEFORE PICK UP</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N33" s="2" t="n">
         <v>0</v>
@@ -3315,22 +3323,22 @@
     <row r="34" ht="13" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902686</t>
+          <t>HASLS22260902633</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>KUS</t>
+          <t>SWAL</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2616N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>202610152100</t>
+          <t>202610220200</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -3341,36 +3349,36 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>TAPIOCA DEVELOPMENT CORP., LTD.</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>TAPIOCA STARCH</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N34" s="2" t="n">
         <v>0</v>
@@ -3400,12 +3408,12 @@
     <row r="35" ht="13" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902725</t>
+          <t>HASLS22260902649</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3415,7 +3423,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>202610201800</t>
+          <t>202610252330</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -3426,166 +3434,166 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPKIJ</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>PACIFIC SUGAR CORPORATION LIMITED</t>
+          <t>TPT PETROCHEMICALS PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>PET RESIN</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD AND CLEAN CONTAINER FOR FOOD</t>
+          <t>Request container good grade, suitable for loading beverage packaging / Pet resin Not bad smell inside container, No rust, No hole inside, Grade A-B</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>HASLS22260902696</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>2615N</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>202610240700</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20OTx1 </t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>20261015</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>GUARDIAN INDUSTRIES CORP LTD.</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>GLASS &amp; GLASS PRODUCTS</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>**DO NOT RELEASE CNTR WAIT APPROVE** [1X20OT OVER 1TEUS O/H 40 CMS]</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="13" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902743</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>SWIC</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>202610152200</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>SANJIANG CHEMICAL FIBER (THAILAND) CO.,LTD</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>POLYESTER STAPLE FIBER</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="2" t="n">
+      <c r="S36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37" ht="13" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902749</t>
+          <t>HASLS22260902701</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>202610201800</t>
+          <t>202610240200</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -3601,17 +3609,17 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3621,7 +3629,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
@@ -3631,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P37" s="2" t="n">
         <v>0</v>
@@ -3655,7 +3663,7 @@
     <row r="38" ht="13" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902750</t>
+          <t>HASLS22260902725</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -3670,7 +3678,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>202610201800</t>
+          <t>202610220200</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -3691,22 +3699,22 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20260914</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>PACIFIC SUGAR CORPORATION LIMITED</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+          <t>REQUEST GOOD AND CLEAN CONTAINER FOR FOOD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
@@ -3740,12 +3748,12 @@
     <row r="39" ht="13" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902819</t>
+          <t>HASLS22260902739</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PGPO</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3755,7 +3763,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>202610160600</t>
+          <t>202610250800</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -3771,17 +3779,17 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx5 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3791,7 +3799,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
@@ -3801,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P39" s="2" t="n">
         <v>0</v>
@@ -3825,22 +3833,22 @@
     <row r="40" ht="13" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000005</t>
+          <t>HASLS22261000107</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>KJT</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>202610191200</t>
+          <t>202610280600</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -3851,22 +3859,22 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>JPNAH</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">20'x10 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3876,11 +3884,11 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>RQST NO RED WALL CONTAINER,CLEAN CONTAINER NO OIL STAINS , NO RUSTY ,NO CUT OR HOLE</t>
+          <t>SURVEY 14/10/2026</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N40" s="2" t="n">
         <v>0</v>
@@ -3910,22 +3918,22 @@
     <row r="41" ht="13" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000008</t>
+          <t>HASLS22261000256</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>KUS</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2616N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>202610152100</t>
+          <t>202610240200</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -3936,7 +3944,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3946,22 +3954,22 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+          <t>WELLGROW GLASS INDUSTRY CO., LTD.</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>POLYAMIDE RESIN</t>
+          <t xml:space="preserve">GLASS BOTTLE </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Sound and Clean</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
@@ -3995,12 +4003,12 @@
     <row r="42" ht="13" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000114</t>
+          <t>HASLS22261000278</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4010,7 +4018,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>202610152200</t>
+          <t>202610240900</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -4021,27 +4029,27 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>SRI TRANG GLOVES (THAILAND) PUBLIC COMPANY LIMITED</t>
+          <t>DOUBLE A (1991) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLOVES </t>
+          <t>PAPER</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -4050,7 +4058,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N42" s="2" t="n">
         <v>0</v>
@@ -4080,22 +4088,22 @@
     <row r="43" ht="13" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000153</t>
+          <t>HASLS22261000285</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SWBT</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2616N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>202610161300</t>
+          <t>202610252330</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -4106,42 +4114,42 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx36 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>INGREDION (THAILAND) CO., LTD.</t>
+          <t>AGC VINYTHAI PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>FOODSTUFFS</t>
+          <t>PVC RESIN</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>A-grade container</t>
+          <t>cntr. food grade</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P43" s="2" t="n">
         <v>0</v>
@@ -4165,22 +4173,22 @@
     <row r="44" ht="13" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000257</t>
+          <t>HASLS22261000340</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>202610201800</t>
+          <t>202610240200</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -4191,42 +4199,43 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x6 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20260930</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>DISH WASHER</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>REQUEST SEA BULK CONTAIER + SURVEY EMPTY BEFORE PICK UP (REQ SURVEY 30/09/2026)</t>
+          <t>*No containers with cut and patch marks inside*
+GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P44" s="2" t="n">
         <v>0</v>
@@ -4250,20 +4259,24 @@
     <row r="45" ht="13" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000307</t>
+          <t>HASLS22261000341</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>TBN</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr"/>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>202610240200</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -4272,42 +4285,43 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>JPTRG</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x9 </t>
+          <t xml:space="preserve">40Hx7 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>REFRIERATOR</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+          <t>*No containers with cut and patch marks inside*
+GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P45" s="2" t="n">
         <v>0</v>
@@ -4331,22 +4345,22 @@
     <row r="46" ht="13" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000346</t>
+          <t>HASLS22261000342</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>KMTP</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>202610150200</t>
+          <t>202610240200</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -4357,42 +4371,43 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx5 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>GENERAL RUBBER (THAILAND) CO., LTD.</t>
+          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>NEW TYRES</t>
+          <t>WASHING MATCHINE</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>*No containers with cut and patch marks inside*
+GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P46" s="2" t="n">
         <v>0</v>
@@ -4416,7 +4431,7 @@
     <row r="47" ht="13" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000407</t>
+          <t>HASLS22261000408</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -4431,7 +4446,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>202610220200</t>
+          <t>202610252330</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -4501,7 +4516,7 @@
     <row r="48" ht="13" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000408</t>
+          <t>HASLS22261000613</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -4516,7 +4531,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>202610220200</t>
+          <t>202610252330</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -4527,7 +4542,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>JPTYO</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4537,22 +4552,22 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>KUBOTA ENGINE ( THAILAND ) CO., LTD.</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>DIESEL ENGINE</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GRADE A CONTAIER + SURVEY EMPTY BEFORE PICK UP DD.15/09/26</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
@@ -4586,22 +4601,22 @@
     <row r="49" ht="13" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000543</t>
+          <t>HASLS22261000614</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>PCCP</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>202610121600</t>
+          <t>202610252330</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -4612,42 +4627,42 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>SHIN SHIN ELECTRONICS(THAILAND) CO., LTD.</t>
+          <t>KUBOTA ENGINE ( THAILAND ) CO., LTD.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>CONNECTION WIRE FOR THERMISTOR SENSOR ASSEMBLY</t>
+          <t>DIESEL ENGINE</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>REQUEST CONTAINER CLEAN &amp; GOOD</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="P49" s="2" t="n">
         <v>0</v>
@@ -4671,22 +4686,22 @@
     <row r="50" ht="13" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000644</t>
+          <t>HASLS22261000695</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>202610201800</t>
+          <t>202610240900</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -4697,36 +4712,36 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNTAO</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261015</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>KUBOTA ENGINE ( THAILAND ) CO., LTD.</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>DIESEL ENGINE</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N50" s="2" t="n">
         <v>0</v>
@@ -4754,189 +4769,104 @@
       </c>
     </row>
     <row r="51" ht="13" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000789</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>KMTP</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>202610150200</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>20261009</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>ANDAMAN METAL CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>COPPER RECYCLE</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>RQST CNTR 32.5 TONS // 40'HQ</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" ht="13" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n"/>
-      <c r="C52" s="3" t="n"/>
-      <c r="D52" s="3" t="n"/>
-      <c r="E52" s="3" t="n"/>
-      <c r="F52" s="3" t="n"/>
-      <c r="G52" s="3" t="n"/>
-      <c r="H52" s="3" t="n"/>
-      <c r="I52" s="3" t="n"/>
-      <c r="J52" s="3" t="n"/>
-      <c r="K52" s="3" t="n"/>
-      <c r="L52" s="3" t="n"/>
-      <c r="M52" s="3">
-        <f>SUM(M2:M51)</f>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4">
+        <f>SUM(M2:M50)</f>
         <v/>
       </c>
-      <c r="N52" s="3">
-        <f>SUM(N2:N51)</f>
+      <c r="N51" s="4">
+        <f>SUM(N2:N50)</f>
         <v/>
       </c>
-      <c r="O52" s="3">
-        <f>SUM(O2:O51)</f>
+      <c r="O51" s="4">
+        <f>SUM(O2:O50)</f>
         <v/>
       </c>
-      <c r="P52" s="3">
-        <f>SUM(P2:P51)</f>
+      <c r="P51" s="4">
+        <f>SUM(P2:P50)</f>
         <v/>
       </c>
-      <c r="Q52" s="3">
-        <f>SUM(Q2:Q51)</f>
+      <c r="Q51" s="4">
+        <f>SUM(Q2:Q50)</f>
         <v/>
       </c>
-      <c r="R52" s="3">
-        <f>SUM(R2:R51)</f>
+      <c r="R51" s="4">
+        <f>SUM(R2:R50)</f>
         <v/>
       </c>
-      <c r="S52" s="3">
-        <f>SUM(S2:S51)</f>
+      <c r="S51" s="4">
+        <f>SUM(S2:S50)</f>
         <v/>
       </c>
-      <c r="T52" s="3">
-        <f>SUM(T2:T51)</f>
+      <c r="T51" s="4">
+        <f>SUM(T2:T50)</f>
         <v/>
       </c>
-      <c r="U52" s="3">
-        <f>SUM(U2:U51)</f>
+      <c r="U51" s="4">
+        <f>SUM(U2:U50)</f>
         <v/>
       </c>
     </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
+      </c>
+    </row>
     <row r="55" ht="13" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>PW DEPOT CO., LTD.</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>184</v>
       </c>
     </row>
     <row r="56" ht="13" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>PW DEPOT CO., LTD.</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="57" ht="13" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B57" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>146</v>
+      <c r="B56" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U51"/>
+  <autoFilter ref="A1:U50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - PW DEPOT CO., LTD.xlsx
+++ b/output/bkg pending - PW DEPOT CO., LTD.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002E75B6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0092D050"/>
       </patternFill>
     </fill>
     <fill>
@@ -97,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -105,13 +100,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -479,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U56"/>
+  <dimension ref="A1:U53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -489,7 +481,7 @@
     <col width="4" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
@@ -615,24 +607,20 @@
     <row r="2" ht="13" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801507</t>
+          <t>HASLS22260801848</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>202610240200</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -641,43 +629,42 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx7 </t>
+          <t xml:space="preserve">20'x3 </t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20260908</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>DISH WASHER</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>*No containers with cut and patch marks inside*
-GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -701,20 +688,24 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260801848</t>
+          <t>HASLS22260900168</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TBN</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>202610262300</t>
+        </is>
+      </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -723,36 +714,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>JPTRG</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x3 </t>
+          <t xml:space="preserve">20'x32 </t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20260908</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>GC-M PTA COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>PURIFIED TEREPHTHALIC ACID (HS CODE: 291736)</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+          <t>SPECIAL REQUEST : SEABULK CONTAINER (FOR TOYOBO SHIPMENT)</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>0</v>
@@ -782,22 +773,22 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900167</t>
+          <t>HASLS22260900175</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>202610240200</t>
+          <t>202610282300</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -808,36 +799,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>JPTRG</t>
+          <t>JPTYO</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x32 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>GC-M PTA COMPANY LIMITED</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>PURIFIED TEREPHTHALIC ACID (HS CODE: 291736)</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SPECIAL REQUEST : SEABULK CONTAINER (FOR TOYOBO SHIPMENT)</t>
+          <t>REQUEST GRADE A CONTAIER + SURVEY EMPTY BEFORE PICK UP DD.15/09/26</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -867,24 +858,20 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900170</t>
+          <t>HASLS22260900547</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>202610252330</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -898,31 +885,31 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x32 </t>
+          <t xml:space="preserve">20'x3 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>GC-M PTA COMPANY LIMITED</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>PURIFIED TEREPHTHALIC ACID (HS CODE: 291736)</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SPECIAL REQUEST : SEABULK CONTAINER (FOR TOYOBO SHIPMENT)</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -952,24 +939,20 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900175</t>
+          <t>HASLS22260900548</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>202610280600</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -978,22 +961,22 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>JPTYO</t>
+          <t>JPTRG</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x11 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20260925</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1003,11 +986,11 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GRADE A CONTAIER + SURVEY EMPTY BEFORE PICK UP DD.15/09/26</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
@@ -1037,7 +1020,7 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900547</t>
+          <t>HASLS22260900550</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1059,17 +1042,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>JPTRG</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x3 </t>
+          <t xml:space="preserve">20'x9 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1088,7 +1071,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1118,7 +1101,7 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900548</t>
+          <t>HASLS22260900551</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1140,17 +1123,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>JPTRG</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x11 </t>
+          <t xml:space="preserve">20'x10 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20260926</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1169,7 +1152,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>0</v>
@@ -1199,20 +1182,24 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900551</t>
+          <t>HASLS22260900767</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>TBN</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>202610282300</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1221,36 +1208,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x10 </t>
+          <t xml:space="preserve">20'x25 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20260926</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>NEW BIODIESEL CO.,LTD.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>PALM OIL IN FLEXIBAG</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+          <t>**APPROVAL BY MR. KIM JAE-HYUNG DD.22/09/2026** *FLEXIBAG*</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="N9" s="2" t="n">
         <v>0</v>
@@ -1280,22 +1267,22 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901417</t>
+          <t>HASLS22260900989</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>YSVY</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>202610220430</t>
+          <t>202610282300</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1306,27 +1293,27 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20260919</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>CCL LABEL (THAI) LTD.</t>
+          <t>TANATEX CHEMICALS (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>STICKER LABEL</t>
+          <t>CHEMICALS PRODUCT (NON DG)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1335,13 +1322,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>0</v>
@@ -1365,22 +1352,22 @@
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901660</t>
+          <t>HASLS22260901009</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>KXM</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2609S</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>202611090200</t>
+          <t>202610251730</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -1391,30 +1378,370 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Good grade or food grade container for WITHOUT PALLET</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901014</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>202610251730</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Good grade or food grade container for WITHOUT PALLET</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901176</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>202610280700</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20261016</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901311</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>HAB</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>202610282300</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx12 </t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901660</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>KXM</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202611090200</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>IDJKT</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>20261005</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>OATSIDE (THAILAND) LIMITED.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>OAT MILK ( GOOD GRADE CONTAINER REQUIRED)</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Good dry and clean container
 Food grade container only
@@ -1422,354 +1749,14 @@
 No Physical Damage.</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="2" t="n">
+      <c r="M15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901703</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>202610240200</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x11 </t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901774</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>202610240700</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20261012</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>ELNA (THAILAND) CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>ELECTROLYTIC CONDENSER SOLUTION</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>**REQ GOOD, CLEAN, NO LEAK AND GRADE A CONTAINER</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902027</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SWIC</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>202610170200</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>JPYKK</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20261005</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1X20' SEABULK</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260902028</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SWIC</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>202610170200</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>JPYKK</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>20261005</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>1X20' SEABULK</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="P15" s="2" t="n">
         <v>0</v>
@@ -1793,24 +1780,20 @@
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902029</t>
+          <t>HASLS22260901945</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>202610170200</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1824,17 +1807,17 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x7 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1844,7 +1827,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
@@ -1878,24 +1861,20 @@
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902030</t>
+          <t>HASLS22260901946</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SWIC</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>202610170200</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1909,17 +1888,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x4 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20261005</t>
+          <t>20260925</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1929,11 +1908,11 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1963,22 +1942,22 @@
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902236</t>
+          <t>HASLS22260902385</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202610252330</t>
+          <t>202610251730</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1989,42 +1968,42 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx6 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+          <t>BERLI JUCKER CELLOX LIMITED</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>POLYAMIDE RESIN</t>
+          <t>TISSUE</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Sound and Clean</t>
+          <t>REQUEST GOOD GRADE CONTAINER</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P18" s="2" t="n">
         <v>0</v>
@@ -2048,22 +2027,22 @@
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902238</t>
+          <t>HASLS22260902488</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>202610252330</t>
+          <t>202610282300</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -2074,42 +2053,42 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20261010</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>POLYAMIDE RESIN</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Sound and Clean</t>
+          <t>REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P19" s="2" t="n">
         <v>0</v>
@@ -2133,22 +2112,22 @@
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902366</t>
+          <t>HASLS22260902492</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>202610240900</t>
+          <t>202610271300</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -2159,22 +2138,22 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x7 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261009</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>THAI POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2184,17 +2163,17 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CTNR</t>
+          <t>REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>0</v>
@@ -2218,22 +2197,22 @@
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902385</t>
+          <t>HASLS22260902504</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>202610240200</t>
+          <t>202610280700</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -2249,37 +2228,37 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx6 </t>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>BERLI JUCKER CELLOX LIMITED</t>
+          <t>TIETEX ASIA LIMITED</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>TISSUE</t>
+          <t>POLYESTER</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD GRADE CONTAINER</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P21" s="2" t="n">
         <v>0</v>
@@ -2303,22 +2282,22 @@
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902435</t>
+          <t>HASLS22260902549</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>202610251100</t>
+          <t>202611042200</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -2329,42 +2308,42 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20260926</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+          <t>THAIXING CIRCUITS CO., LTD.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">POLYAMIDE RESIN </t>
+          <t>MULTILAYER PRINTED CIRCUIT BOARD</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Sound and Clean</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="P22" s="2" t="n">
         <v>0</v>
@@ -2388,22 +2367,22 @@
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902451</t>
+          <t>HASLS22261000008</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>NSSJ</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>202610251100</t>
+          <t>202610262300</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -2414,7 +2393,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2424,7 +2403,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2434,7 +2413,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">POLYAMIDE RESIN </t>
+          <t>POLYAMIDE RESIN</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2473,22 +2452,22 @@
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902492</t>
+          <t>HASLS22261000084</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>202610252330</t>
+          <t>202610282300</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -2499,22 +2478,22 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>JPKMJ</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x6 </t>
+          <t xml:space="preserve">20'x3 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2524,11 +2503,11 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY</t>
+          <t>GOOD AND CLEAN CONTAINERS</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
@@ -2558,22 +2537,22 @@
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902549</t>
+          <t>HASLS22261000171</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>202611021800</t>
+          <t>202610282300</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -2584,27 +2563,27 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20260926</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>THAIXING CIRCUITS CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>MULTILAYER PRINTED CIRCUIT BOARD</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2613,13 +2592,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="2" t="n">
         <v>0</v>
@@ -2643,12 +2622,12 @@
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902590</t>
+          <t>HASLS22261000172</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2658,7 +2637,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>202610250800</t>
+          <t>202610282300</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -2669,36 +2648,36 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x8 </t>
+          <t xml:space="preserve">20'x11 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>SRI TRANG AGRO-INDUSTRY PUBLIC COMPANY LIMITED</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>NATURAL RUBBER STR20</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Grade B container with Strong wooden floor for heavy cargo and without wood splinter,Use Forklift to stuffing the cargo into the container</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2728,12 +2707,12 @@
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902595</t>
+          <t>HASLS22261000344</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2743,7 +2722,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>202610250800</t>
+          <t>202610280700</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -2754,22 +2733,22 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>JPMYJ</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2779,17 +2758,17 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>*** GOOD &amp; CLEAN CONT. &amp; GRADE A ***</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P27" s="2" t="n">
         <v>0</v>
@@ -2813,22 +2792,22 @@
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902625</t>
+          <t>HASLS22261000345</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>202610220200</t>
+          <t>202610280700</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -2849,7 +2828,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2898,22 +2877,22 @@
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902626</t>
+          <t>HASLS22261000347</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>202610220200</t>
+          <t>202610280700</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -2934,7 +2913,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2983,22 +2962,22 @@
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902627</t>
+          <t>HASLS22261000348</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>202610220200</t>
+          <t>202610282300</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -3009,7 +2988,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3019,7 +2998,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3068,22 +3047,22 @@
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902630</t>
+          <t>HASLS22261000349</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>202610220200</t>
+          <t>202610282300</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -3104,7 +3083,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3153,12 +3132,12 @@
     <row r="32" ht="13" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902631</t>
+          <t>HASLS22261000396</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3168,7 +3147,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>202610220200</t>
+          <t>202610271300</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -3179,7 +3158,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3189,22 +3168,22 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>DAECHANG TRADING (THAILAND) CO.,LTD.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>BRASS ROD</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>REQUEST GOOD &amp; CLEAN CONTAINER / WITHOUT HOLE</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
@@ -3238,22 +3217,22 @@
     <row r="33" ht="13" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902632</t>
+          <t>HASLS22261000411</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>202610220200</t>
+          <t>202611041200</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -3274,7 +3253,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -3323,22 +3302,22 @@
     <row r="34" ht="13" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902633</t>
+          <t>HASLS22261000414</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>202610220200</t>
+          <t>202611041200</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -3359,7 +3338,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3408,22 +3387,22 @@
     <row r="35" ht="13" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902649</t>
+          <t>HASLS22261000643</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>202610252330</t>
+          <t>202610280700</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -3434,7 +3413,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>JPKIJ</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3444,22 +3423,22 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>TPT PETROCHEMICALS PUBLIC COMPANY LIMITED</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>PET RESIN</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Request container good grade, suitable for loading beverage packaging / Pet resin Not bad smell inside container, No rust, No hole inside, Grade A-B</t>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
@@ -3491,109 +3470,109 @@
       </c>
     </row>
     <row r="36" ht="13" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>HASLS22260902696</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>CMA</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>2615N</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>202610240700</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22261000707</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>HAB</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>202610282300</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>THLCH</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>CNSHK</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20OTx1 </t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>GUARDIAN INDUSTRIES CORP LTD.</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>GLASS &amp; GLASS PRODUCTS</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>**DO NOT RELEASE CNTR WAIT APPROVE** [1X20OT OVER 1TEUS O/H 40 CMS]</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="3" t="n">
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>20261020</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>KUBOTA ENGINE ( THAILAND ) CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>DIESEL ENGINE</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="3" t="n">
+      <c r="N36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37" ht="13" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902701</t>
+          <t>HASLS22261000813</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>202610240200</t>
+          <t>202610241900</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -3604,32 +3583,32 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">40Hx12 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261017</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>KURARAY CO., LTD.</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>GENESTAR</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>GOOD DRY AND CLEAN CONTAINER.</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
@@ -3639,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P37" s="2" t="n">
         <v>0</v>
@@ -3663,22 +3642,22 @@
     <row r="38" ht="13" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902725</t>
+          <t>HASLS22261000969</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SWAL</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>202610220200</t>
+          <t>202610282300</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -3689,42 +3668,42 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx6 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20260914</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>PACIFIC SUGAR CORPORATION LIMITED</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD AND CLEAN CONTAINER FOR FOOD</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P38" s="2" t="n">
         <v>0</v>
@@ -3748,7 +3727,7 @@
     <row r="39" ht="13" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902739</t>
+          <t>HASLS22261000979</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -3763,7 +3742,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>202610250800</t>
+          <t>202610262300</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -3779,27 +3758,27 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx5 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>HUAYI GROUP (THAILAND) COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>NEW TIRE</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQUEST GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
@@ -3809,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P39" s="2" t="n">
         <v>0</v>
@@ -3833,12 +3812,12 @@
     <row r="40" ht="13" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000107</t>
+          <t>HASLS22261000991</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3848,7 +3827,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>202610280600</t>
+          <t>202610262300</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -3859,42 +3838,42 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x10 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>MAXXIS INTERNATIONAL (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>TIRES</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SURVEY 14/10/2026</t>
+          <t>REQUEST CONTAINER GOOD GRADE</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P40" s="2" t="n">
         <v>0</v>
@@ -3918,22 +3897,22 @@
     <row r="41" ht="13" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000256</t>
+          <t>HASLS22261001118</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>202610240200</t>
+          <t>202610271300</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -3944,42 +3923,42 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>WELLGROW GLASS INDUSTRY CO., LTD.</t>
+          <t>FIRST MATERIAL SCIENCE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLASS BOTTLE </t>
+          <t xml:space="preserve">ETHYLENE VINYL ACETATE RESIN </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQUEST GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P41" s="2" t="n">
         <v>0</v>
@@ -4003,22 +3982,22 @@
     <row r="42" ht="13" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000278</t>
+          <t>HASLS22261001128</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>202610240900</t>
+          <t>202610251730</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -4029,27 +4008,27 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>DOUBLE A (1991) PUBLIC COMPANY LIMITED</t>
+          <t>AVERY DENNISON (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>PAPER</t>
+          <t>PAPER/FILM</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -4058,13 +4037,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="N42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="P42" s="2" t="n">
         <v>0</v>
@@ -4088,22 +4067,22 @@
     <row r="43" ht="13" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000285</t>
+          <t>HASLS22261001424</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>202610252330</t>
+          <t>202610241900</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -4114,32 +4093,32 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx36 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20261015</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>AGC VINYTHAI PUBLIC COMPANY LIMITED</t>
+          <t>THAI GULF JELLYFISH CO., LTD.</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>PVC RESIN</t>
+          <t>SALTED JELLYFISH</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>cntr. food grade</t>
+          <t>UNDER DECK &amp; AWAYS FROM HOT AREA"</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
@@ -4149,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="P43" s="2" t="n">
         <v>0</v>
@@ -4173,22 +4152,22 @@
     <row r="44" ht="13" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000340</t>
+          <t>HASLS22261001499</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>CMA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2615N</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>202610240200</t>
+          <t>202610260100</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -4199,43 +4178,42 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>CNSHK</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">20'x4 </t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>DISH WASHER</t>
+          <t xml:space="preserve">POLYAMIDE RESIN </t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>*No containers with cut and patch marks inside*
-GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
+          <t>RQST CNTR GRADE A</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P44" s="2" t="n">
         <v>0</v>
@@ -4259,22 +4237,22 @@
     <row r="45" ht="13" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000341</t>
+          <t>HASLS22261001518</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2613N</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>202610240200</t>
+          <t>202611190400</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -4285,43 +4263,42 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx7 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
+          <t>BASF (THAI) LIMITED</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>REFRIERATOR</t>
+          <t>TEXAPON N 70 AC 1 (NON DG)</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>*No containers with cut and patch marks inside*
-GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
+          <t>**REQUESTED FOR GOOD CNTR WITH NO HOLE / NO RUST / NO BURR / NOT WET / NO BAD SMELL**</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P45" s="2" t="n">
         <v>0</v>
@@ -4345,12 +4322,12 @@
     <row r="46" ht="13" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000342</t>
+          <t>HASLS22261001519</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4360,7 +4337,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>202610240200</t>
+          <t>202611230830</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -4371,43 +4348,42 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>KRPTK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx5 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
+          <t>BASF (THAI) LIMITED</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>WASHING MATCHINE</t>
+          <t>TEXAPON N 70 AC 1 (NON DG)</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>*No containers with cut and patch marks inside*
-GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
+          <t>**REQUESTED FOR GOOD CNTR WITH NO HOLE / NO RUST / NO BURR / NOT WET / NO BAD SMELL**</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P46" s="2" t="n">
         <v>0</v>
@@ -4431,22 +4407,22 @@
     <row r="47" ht="13" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000408</t>
+          <t>HASLS22261001539</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>202610252330</t>
+          <t>202610262300</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -4457,42 +4433,42 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>JPTYO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>PKT PLUS CO.,LTD</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>SYRUP</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GRADE A CONTAIER + SURVEY EMPTY BEFORE PICK UP DD.15/09/26</t>
+          <t>UPGRADE CNTR / CLEAN CONTAINER AND CONTAINER GOOD CONDITION</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P47" s="2" t="n">
         <v>0</v>
@@ -4514,359 +4490,104 @@
       </c>
     </row>
     <row r="48" ht="13" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000613</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>HMVY</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>202610252330</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>KUBOTA ENGINE ( THAILAND ) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>DIESEL ENGINE</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" ht="13" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000614</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>HMVY</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>202610252330</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>20261014</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>KUBOTA ENGINE ( THAILAND ) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>DIESEL ENGINE</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" ht="13" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000695</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>KMGY</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>202610240900</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>CNTAO</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>20261015</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>KUBOTA ENGINE ( THAILAND ) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>DIESEL ENGINE</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="2" t="n">
-        <v>0</v>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n"/>
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="3" t="n"/>
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" s="3" t="n"/>
+      <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="n"/>
+      <c r="L48" s="3" t="n"/>
+      <c r="M48" s="3">
+        <f>SUM(M2:M47)</f>
+        <v/>
+      </c>
+      <c r="N48" s="3">
+        <f>SUM(N2:N47)</f>
+        <v/>
+      </c>
+      <c r="O48" s="3">
+        <f>SUM(O2:O47)</f>
+        <v/>
+      </c>
+      <c r="P48" s="3">
+        <f>SUM(P2:P47)</f>
+        <v/>
+      </c>
+      <c r="Q48" s="3">
+        <f>SUM(Q2:Q47)</f>
+        <v/>
+      </c>
+      <c r="R48" s="3">
+        <f>SUM(R2:R47)</f>
+        <v/>
+      </c>
+      <c r="S48" s="3">
+        <f>SUM(S2:S47)</f>
+        <v/>
+      </c>
+      <c r="T48" s="3">
+        <f>SUM(T2:T47)</f>
+        <v/>
+      </c>
+      <c r="U48" s="3">
+        <f>SUM(U2:U47)</f>
+        <v/>
       </c>
     </row>
     <row r="51" ht="13" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
-      <c r="J51" s="4" t="n"/>
-      <c r="K51" s="4" t="n"/>
-      <c r="L51" s="4" t="n"/>
-      <c r="M51" s="4">
-        <f>SUM(M2:M50)</f>
-        <v/>
-      </c>
-      <c r="N51" s="4">
-        <f>SUM(N2:N50)</f>
-        <v/>
-      </c>
-      <c r="O51" s="4">
-        <f>SUM(O2:O50)</f>
-        <v/>
-      </c>
-      <c r="P51" s="4">
-        <f>SUM(P2:P50)</f>
-        <v/>
-      </c>
-      <c r="Q51" s="4">
-        <f>SUM(Q2:Q50)</f>
-        <v/>
-      </c>
-      <c r="R51" s="4">
-        <f>SUM(R2:R50)</f>
-        <v/>
-      </c>
-      <c r="S51" s="4">
-        <f>SUM(S2:S50)</f>
-        <v/>
-      </c>
-      <c r="T51" s="4">
-        <f>SUM(T2:T50)</f>
-        <v/>
-      </c>
-      <c r="U51" s="4">
-        <f>SUM(U2:U50)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="13" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
           <t>Pickup Name</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Number of Records</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Total Balance</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="13" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>PW DEPOT CO., LTD.</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="56" ht="13" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="B52" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B56" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>184</v>
+      <c r="B53" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U50"/>
+  <autoFilter ref="A1:U47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - PW DEPOT CO., LTD.xlsx
+++ b/output/bkg pending - PW DEPOT CO., LTD.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U53"/>
+  <dimension ref="A1:U52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -688,24 +688,20 @@
     <row r="3" ht="13" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900168</t>
+          <t>HASLS22260900547</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>202610262300</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -719,31 +715,31 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x32 </t>
+          <t xml:space="preserve">20'x3 </t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>GC-M PTA COMPANY LIMITED</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>PURIFIED TEREPHTHALIC ACID (HS CODE: 291736)</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SPECIAL REQUEST : SEABULK CONTAINER (FOR TOYOBO SHIPMENT)</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>0</v>
@@ -773,24 +769,20 @@
     <row r="4" ht="13" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900175</t>
+          <t>HASLS22260900548</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>202610282300</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -799,22 +791,22 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>JPTYO</t>
+          <t>JPTRG</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x11 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20260925</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -824,11 +816,11 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GRADE A CONTAIER + SURVEY EMPTY BEFORE PICK UP DD.15/09/26</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>0</v>
@@ -858,7 +850,7 @@
     <row r="5" ht="13" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900547</t>
+          <t>HASLS22260900550</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -880,17 +872,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>JPTRG</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x3 </t>
+          <t xml:space="preserve">20'x9 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260917</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -909,7 +901,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>0</v>
@@ -939,7 +931,7 @@
     <row r="6" ht="13" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900548</t>
+          <t>HASLS22260900551</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -961,17 +953,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>JPTRG</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x11 </t>
+          <t xml:space="preserve">20'x10 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20260926</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -990,7 +982,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>0</v>
@@ -1020,20 +1012,24 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900550</t>
+          <t>HASLS22260900767</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TBN</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>202610282300</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -1042,36 +1038,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x9 </t>
+          <t xml:space="preserve">20'x25 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20260917</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>NEW BIODIESEL CO.,LTD.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>PALM OIL IN FLEXIBAG</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+          <t>**APPROVAL BY MR. KIM JAE-HYUNG DD.22/09/2026** *FLEXIBAG*</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>0</v>
@@ -1101,20 +1097,24 @@
     <row r="8" ht="13" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900551</t>
+          <t>HASLS22260901660</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TBN</t>
+          <t>KXM</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
+          <t>2609S</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>202611130200</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -1123,625 +1123,30 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x10 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20260926</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>OATSIDE (THAILAND) LIMITED.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>OAT MILK ( GOOD GRADE CONTAINER REQUIRED)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>RQST CNTR SEABULK &amp; GRADE A</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="13" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260900767</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>HAB</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>202610282300</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x25 </t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>20261016</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>NEW BIODIESEL CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>PALM OIL IN FLEXIBAG</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>**APPROVAL BY MR. KIM JAE-HYUNG DD.22/09/2026** *FLEXIBAG*</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="13" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260900989</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>HAB</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>202610282300</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x2 </t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20261020</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>TANATEX CHEMICALS (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>CHEMICALS PRODUCT (NON DG)</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901009</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>202610251730</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>20261016</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>Good grade or food grade container for WITHOUT PALLET</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901014</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>202610251730</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>20261016</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>Good grade or food grade container for WITHOUT PALLET</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901176</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>HAHM</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>202610280700</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20261016</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901311</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>HAB</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>202610282300</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx12 </t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20261020</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901660</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>KXM</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>202611090200</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx3 </t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>20261005</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>OATSIDE (THAILAND) LIMITED.</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>OAT MILK ( GOOD GRADE CONTAINER REQUIRED)</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Good dry and clean container
 Food grade container only
@@ -1749,6 +1154,593 @@
 No Physical Damage.</t>
         </is>
       </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="13" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901815</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>202611041600</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>JPOSA</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>GLOBAL GREEN CHEMICALS PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REFINED GLYCERINE 99.5% USP </t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="13" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901945</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>TBN</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>JPYKK</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x7 </t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="13" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901946</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>TBN</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>JPYKK</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x4 </t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>RESIN</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="13" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901992</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SWMM</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>202610251500</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>KRKAN</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx2 </t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>THAI YOOWON ELECTRONICS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>EVAPORATOR</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="13" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902363</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>HAB</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>202610282300</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>CNSHA</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>AGC VINYTHAI PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>PVC RESIN</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>NEW CNTR, GRADE A</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="13" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902504</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>HAHM</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2612N</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>202610280700</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>VNSGN</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 20'x1 </t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>TIETEX ASIA LIMITED</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>POLYESTER</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="13" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260902549</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202611041600</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>CNSHK</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40Hx1 </t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>20260926</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>THAIXING CIRCUITS CO., LTD.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>MULTILAYER PRINTED CIRCUIT BOARD</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
       </c>
@@ -1756,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P15" s="2" t="n">
         <v>0</v>
@@ -1780,20 +1772,24 @@
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901945</t>
+          <t>HASLS22261000008</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>TBN</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr"/>
+          <t>2609N</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>202610271900</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1802,32 +1798,32 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x7 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>POLYAMIDE RESIN</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+          <t>Sound and Clean</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
@@ -1861,20 +1857,24 @@
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901946</t>
+          <t>HASLS22261000040</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>TBN</t>
+          <t>KMSU</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr"/>
+          <t>2608S</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>202611012100</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1883,36 +1883,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x4 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>QUAKER HOUGHTON (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>QUAKERCOOL 2770 PLUS</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+          <t>DG22GPx1 (CLS 9 / UN 3082)</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1942,22 +1942,22 @@
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902385</t>
+          <t>HASLS22261000171</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202610251730</t>
+          <t>202610282300</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1968,32 +1968,32 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx6 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>BERLI JUCKER CELLOX LIMITED</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>TISSUE</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD GRADE CONTAINER</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P18" s="2" t="n">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902488</t>
+          <t>HASLS22261000172</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">40Hx6 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
@@ -2088,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P19" s="2" t="n">
         <v>0</v>
@@ -2112,22 +2112,22 @@
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902492</t>
+          <t>HASLS22261000205</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>202610271300</t>
+          <t>202611041600</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -2138,22 +2138,22 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>JPIYM</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20261009</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>THAI POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2163,17 +2163,17 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>REQ GOOD AND CLEAN CONT., NO OIL, NO RUSTY</t>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>0</v>
@@ -2197,22 +2197,22 @@
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902504</t>
+          <t>HASLS22261000344</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>202610280700</t>
+          <t>202610271900</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2238,17 +2238,17 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>TIETEX ASIA LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>POLYESTER</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
@@ -2258,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" s="2" t="n">
         <v>0</v>
@@ -2282,22 +2282,22 @@
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902549</t>
+          <t>HASLS22261000345</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>202611042200</t>
+          <t>202610271900</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -2308,42 +2308,42 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20260926</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>THAIXING CIRCUITS CO., LTD.</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>MULTILAYER PRINTED CIRCUIT BOARD</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" s="2" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000008</t>
+          <t>HASLS22261000347</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>202610262300</t>
+          <t>202610271900</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2408,17 +2408,17 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>POLYAMIDE RESIN</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Sound and Clean</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
@@ -2452,7 +2452,7 @@
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000084</t>
+          <t>HASLS22261000348</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>JPKMJ</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x3 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINERS</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
@@ -2537,7 +2537,7 @@
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000171</t>
+          <t>HASLS22261000349</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2563,22 +2563,22 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x5 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2588,11 +2588,11 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2622,22 +2622,22 @@
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000172</t>
+          <t>HASLS22261000396</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>202610282300</t>
+          <t>202610271900</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -2653,31 +2653,31 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x11 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>DAECHANG TRADING (THAILAND) CO.,LTD.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>BRASS ROD</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQUEST GOOD &amp; CLEAN CONTAINER / WITHOUT HOLE</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
@@ -2707,22 +2707,22 @@
     <row r="27" ht="13" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000344</t>
+          <t>HASLS22261000411</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>202610280700</t>
+          <t>202611041200</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2792,22 +2792,22 @@
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000345</t>
+          <t>HASLS22261000414</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>202610280700</t>
+          <t>202611041200</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000347</t>
+          <t>HASLS22261000491</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>202610280700</t>
+          <t>202610262300</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -2903,32 +2903,32 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>BEN TECH CHEMICAL CO.,LTD.</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>DYEING AUXILIARY FOR TEXTILE</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CTNR</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
@@ -2962,12 +2962,12 @@
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000348</t>
+          <t>HASLS22261000603</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>202610282300</t>
+          <t>202611101600</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -2988,22 +2988,22 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>JPUKB</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x7 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -3013,11 +3013,11 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>SEA BULK CTNR // SURVEY DD.21/10</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N30" s="2" t="n">
         <v>0</v>
@@ -3047,22 +3047,22 @@
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000349</t>
+          <t>HASLS22261000650</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>DJCF</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>0153N</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>202610282300</t>
+          <t>202611031700</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -3073,42 +3073,43 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>KRPTK</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>AIR CONDTIONER</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>No containers with cut and patch marks inside*
+GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P31" s="2" t="n">
         <v>0</v>
@@ -3132,22 +3133,22 @@
     <row r="32" ht="13" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000396</t>
+          <t>HASLS22261000813</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>KMGY</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>202610271300</t>
+          <t>202610241900</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -3158,42 +3159,42 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx12 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261017</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>DAECHANG TRADING (THAILAND) CO.,LTD.</t>
+          <t>KURARAY CO., LTD.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>BRASS ROD</t>
+          <t>GENESTAR</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD &amp; CLEAN CONTAINER / WITHOUT HOLE</t>
+          <t>GOOD DRY AND CLEAN CONTAINER.</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="N32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="P32" s="2" t="n">
         <v>0</v>
@@ -3217,12 +3218,12 @@
     <row r="33" ht="13" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000411</t>
+          <t>HASLS22261000849</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3232,7 +3233,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>202611041200</t>
+          <t>202610251500</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -3243,7 +3244,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3253,22 +3254,22 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>AJ PLAST PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>BOPP FILM</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>Request container upgrade 32.5 tons Dry ,clean and good condition containers (grade A for food grade)</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
@@ -3302,22 +3303,22 @@
     <row r="34" ht="13" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000414</t>
+          <t>HASLS22261000905</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SWSP</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>202611041200</t>
+          <t>202610262300</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -3328,36 +3329,36 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>XIAO XIANG CHEMICAL INDUSTRY (THAILAND) CO.,LTD.</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>ZINC INGOT</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N34" s="2" t="n">
         <v>0</v>
@@ -3387,12 +3388,12 @@
     <row r="35" ht="13" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000643</t>
+          <t>HASLS22261000969</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3402,7 +3403,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>202610280700</t>
+          <t>202610282300</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -3413,17 +3414,17 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x2 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -3438,17 +3439,17 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P35" s="2" t="n">
         <v>0</v>
@@ -3472,22 +3473,22 @@
     <row r="36" ht="13" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000707</t>
+          <t>HASLS22261001009</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>SWBT</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2618N</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>202610282300</t>
+          <t>202611082000</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -3498,36 +3499,36 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>JPYOK</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>KUBOTA ENGINE ( THAILAND ) CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>DIESEL ENGINE</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>SEA BULK CTNR // SURVEY DD.21/10</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N36" s="2" t="n">
         <v>0</v>
@@ -3557,22 +3558,22 @@
     <row r="37" ht="13" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000813</t>
+          <t>HASLS22261001118</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>202610241900</t>
+          <t>202610271900</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -3583,32 +3584,32 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>HKHKG</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx12 </t>
+          <t xml:space="preserve">40Hx4 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>20261017</t>
+          <t>20261020</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>KURARAY CO., LTD.</t>
+          <t>FIRST MATERIAL SCIENCE (THAILAND) CO., LTD.</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>GENESTAR</t>
+          <t xml:space="preserve">ETHYLENE VINYL ACETATE RESIN </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>GOOD DRY AND CLEAN CONTAINER.</t>
+          <t>REQUEST GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
@@ -3618,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P37" s="2" t="n">
         <v>0</v>
@@ -3642,12 +3643,12 @@
     <row r="38" ht="13" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000969</t>
+          <t>HASLS22261001236</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>KMBK</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3657,7 +3658,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>202610282300</t>
+          <t>202610262300</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -3668,32 +3669,32 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx6 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>KURARAY GC ADVANCED MATERIALS CO.,LTD.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>GENESTAR</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>REQ. GOOD, CLEAN &amp; DRY GRADE A CONTAINER.</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
@@ -3703,7 +3704,7 @@
         <v>0</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P38" s="2" t="n">
         <v>0</v>
@@ -3727,12 +3728,12 @@
     <row r="39" ht="13" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000979</t>
+          <t>HASLS22261001455</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3742,7 +3743,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>202610262300</t>
+          <t>202610280700</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -3758,27 +3759,27 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">40Hx7 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>HUAYI GROUP (THAILAND) COMPANY LIMITED</t>
+          <t>VANACHAI GROUP PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>NEW TIRE</t>
+          <t>PARTICLE BOARD</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD AND CLEAN CONTAINER</t>
+          <t>RQST CNGR 32.5 TONS</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
@@ -3788,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P39" s="2" t="n">
         <v>0</v>
@@ -3812,12 +3813,12 @@
     <row r="40" ht="13" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000991</t>
+          <t>HASLS22261001467</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>KMBK</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3827,7 +3828,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>202610262300</t>
+          <t>202610282300</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -3838,32 +3839,32 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx3 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>MAXXIS INTERNATIONAL (THAILAND) CO., LTD.</t>
+          <t>FUZIN PLASTIC CO.,LTD.</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>TIRES</t>
+          <t>PE RECYCLE PELLET</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>REQUEST CONTAINER GOOD GRADE</t>
+          <t>RQST CNTR 32.5 TONS // 40'HQ</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
@@ -3897,22 +3898,22 @@
     <row r="41" ht="13" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261001118</t>
+          <t>HASLS22261001615</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>202610271300</t>
+          <t>202610282300</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -3928,27 +3929,27 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx4 </t>
+          <t xml:space="preserve">40Hx6 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>FIRST MATERIAL SCIENCE (THAILAND) CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETHYLENE VINYL ACETATE RESIN </t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD AND CLEAN CONTAINER</t>
+          <t>RQST GOOD &amp; CLEAN CNTR</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
@@ -3958,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P41" s="2" t="n">
         <v>0</v>
@@ -3982,22 +3983,22 @@
     <row r="42" ht="13" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261001128</t>
+          <t>HASLS22261001616</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>202610251730</t>
+          <t>202610282300</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -4008,7 +4009,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -4018,22 +4019,22 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>AVERY DENNISON (THAILAND) LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>PAPER/FILM</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>RQST GOOD &amp; CLEAN CNTR</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
@@ -4043,7 +4044,7 @@
         <v>0</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P42" s="2" t="n">
         <v>0</v>
@@ -4067,22 +4068,22 @@
     <row r="43" ht="13" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261001424</t>
+          <t>HASLS22261001632</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>KMGY</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>202610241900</t>
+          <t>202610282300</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -4093,32 +4094,32 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>KRINC</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">40Hx30 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>THAI GULF JELLYFISH CO., LTD.</t>
+          <t>SHUN YI INTERNATIONAL TRADING CO., LTD.</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>SALTED JELLYFISH</t>
+          <t>PAPER PULP</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>UNDER DECK &amp; AWAYS FROM HOT AREA"</t>
+          <t>RQST CNTR 32.5 TONS // 40'HQ</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
@@ -4128,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P43" s="2" t="n">
         <v>0</v>
@@ -4152,22 +4153,22 @@
     <row r="44" ht="13" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261001499</t>
+          <t>HASLS22261001704</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CMA</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2615N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>202610260100</t>
+          <t>202611020200</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -4178,42 +4179,42 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>HKHKG</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x4 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+          <t>UMC ELECTRONICS (THAILAND) LTD.</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">POLYAMIDE RESIN </t>
+          <t xml:space="preserve"> PCBA (8537.20.29)</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>RQST CNTR GRADE A</t>
+          <t>good and clean container</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" s="2" t="n">
         <v>0</v>
@@ -4237,22 +4238,22 @@
     <row r="45" ht="13" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261001518</t>
+          <t>HASLS22261001710</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2613N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>202611190400</t>
+          <t>202610282300</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -4263,42 +4264,42 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>BASF (THAI) LIMITED</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>TEXAPON N 70 AC 1 (NON DG)</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>**REQUESTED FOR GOOD CNTR WITH NO HOLE / NO RUST / NO BURR / NOT WET / NO BAD SMELL**</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P45" s="2" t="n">
         <v>0</v>
@@ -4322,12 +4323,12 @@
     <row r="46" ht="13" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261001519</t>
+          <t>HASLS22261001714</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>SWMM</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4337,7 +4338,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>202611230830</t>
+          <t>202610251500</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -4358,22 +4359,22 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>BASF (THAI) LIMITED</t>
+          <t>ALUCON PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>TEXAPON N 70 AC 1 (NON DG)</t>
+          <t>ALUMINIUM CANS (EMPTY)</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>**REQUESTED FOR GOOD CNTR WITH NO HOLE / NO RUST / NO BURR / NOT WET / NO BAD SMELL**</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
@@ -4405,189 +4406,104 @@
       </c>
     </row>
     <row r="47" ht="13" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261001539</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>KMBK</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>202610262300</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>20261020</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>PKT PLUS CO.,LTD</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>SYRUP</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>UPGRADE CNTR / CLEAN CONTAINER AND CONTAINER GOOD CONDITION</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" ht="13" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
-      <c r="E48" s="3" t="n"/>
-      <c r="F48" s="3" t="n"/>
-      <c r="G48" s="3" t="n"/>
-      <c r="H48" s="3" t="n"/>
-      <c r="I48" s="3" t="n"/>
-      <c r="J48" s="3" t="n"/>
-      <c r="K48" s="3" t="n"/>
-      <c r="L48" s="3" t="n"/>
-      <c r="M48" s="3">
-        <f>SUM(M2:M47)</f>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="n"/>
+      <c r="L47" s="3" t="n"/>
+      <c r="M47" s="3">
+        <f>SUM(M2:M46)</f>
         <v/>
       </c>
-      <c r="N48" s="3">
-        <f>SUM(N2:N47)</f>
+      <c r="N47" s="3">
+        <f>SUM(N2:N46)</f>
         <v/>
       </c>
-      <c r="O48" s="3">
-        <f>SUM(O2:O47)</f>
+      <c r="O47" s="3">
+        <f>SUM(O2:O46)</f>
         <v/>
       </c>
-      <c r="P48" s="3">
-        <f>SUM(P2:P47)</f>
+      <c r="P47" s="3">
+        <f>SUM(P2:P46)</f>
         <v/>
       </c>
-      <c r="Q48" s="3">
-        <f>SUM(Q2:Q47)</f>
+      <c r="Q47" s="3">
+        <f>SUM(Q2:Q46)</f>
         <v/>
       </c>
-      <c r="R48" s="3">
-        <f>SUM(R2:R47)</f>
+      <c r="R47" s="3">
+        <f>SUM(R2:R46)</f>
         <v/>
       </c>
-      <c r="S48" s="3">
-        <f>SUM(S2:S47)</f>
+      <c r="S47" s="3">
+        <f>SUM(S2:S46)</f>
         <v/>
       </c>
-      <c r="T48" s="3">
-        <f>SUM(T2:T47)</f>
+      <c r="T47" s="3">
+        <f>SUM(T2:T46)</f>
         <v/>
       </c>
-      <c r="U48" s="3">
-        <f>SUM(U2:U47)</f>
+      <c r="U47" s="3">
+        <f>SUM(U2:U46)</f>
         <v/>
       </c>
     </row>
+    <row r="50" ht="13" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
+      </c>
+    </row>
     <row r="51" ht="13" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>PW DEPOT CO., LTD.</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>134</v>
       </c>
     </row>
     <row r="52" ht="13" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>PW DEPOT CO., LTD.</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="53" ht="13" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B53" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>173</v>
+      <c r="B52" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U47"/>
+  <autoFilter ref="A1:U46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/bkg pending - PW DEPOT CO., LTD.xlsx
+++ b/output/bkg pending - PW DEPOT CO., LTD.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending'!$A$1:$U$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U52"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <col width="4" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
@@ -1012,22 +1012,22 @@
     <row r="7" ht="13" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260900767</t>
+          <t>HASLS22260901660</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>KXM</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2609S</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>202610282300</t>
+          <t>202611130200</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -1038,115 +1038,30 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>IDJKT</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x25 </t>
+          <t xml:space="preserve">40Hx3 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261005</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>NEW BIODIESEL CO.,LTD.</t>
+          <t>OATSIDE (THAILAND) LIMITED.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>PALM OIL IN FLEXIBAG</t>
+          <t>OAT MILK ( GOOD GRADE CONTAINER REQUIRED)</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>**APPROVAL BY MR. KIM JAE-HYUNG DD.22/09/2026** *FLEXIBAG*</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22260901660</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>KXM</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2609S</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>202611130200</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>IDJKT</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx3 </t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20261005</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>OATSIDE (THAILAND) LIMITED.</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>OAT MILK ( GOOD GRADE CONTAINER REQUIRED)</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Good dry and clean container
 Food grade container only
@@ -1154,14 +1069,99 @@
 No Physical Damage.</t>
         </is>
       </c>
+      <c r="M7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="13" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>HASLS22260901815</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SWAT</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2611N</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>202611050900</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>THLCH</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>JPOSA</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20'x1 </t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20261021</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>GLOBAL GREEN CHEMICALS PUBLIC COMPANY LIMITED</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REFINED GLYCERINE 99.5% USP </t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>GOOD AND CLEAN CONTAINER</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>0</v>
@@ -1185,24 +1185,20 @@
     <row r="9" ht="13" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901815</t>
+          <t>HASLS22260901945</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>TBN</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>202611041600</t>
-        </is>
-      </c>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1211,32 +1207,32 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>JPOSA</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x7 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20260924</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>GLOBAL GREEN CHEMICALS PUBLIC COMPANY LIMITED</t>
+          <t>DOW CHEMICAL THAILAND LTD.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">REFINED GLYCERINE 99.5% USP </t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>RQST CNTR SEABULK &amp; GRADE A</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
@@ -1270,7 +1266,7 @@
     <row r="10" ht="13" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901945</t>
+          <t>HASLS22260901946</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1297,12 +1293,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x7 </t>
+          <t xml:space="preserve">20'x4 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20260924</t>
+          <t>20260925</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1321,7 +1317,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>0</v>
@@ -1351,20 +1347,24 @@
     <row r="11" ht="13" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901946</t>
+          <t>HASLS22261000078</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TBN</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>001</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr"/>
+          <t>2610N</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>202611082100</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1373,36 +1373,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>JPOSA</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x4 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20260925</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>DOW CHEMICAL THAILAND LTD.</t>
+          <t>GLOBAL GREEN CHEMICALS PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t xml:space="preserve">REFINED GLYCERINE 99.5% USP </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>RQST CNTR SEABULK &amp; GRADE A</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>0</v>
@@ -1432,22 +1432,22 @@
     <row r="12" ht="13" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260901992</t>
+          <t>HASLS22261000172</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SWMM</t>
+          <t>HAB</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2610N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>202610251500</t>
+          <t>202610290200</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1458,27 +1458,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>KRKAN</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx2 </t>
+          <t xml:space="preserve">40Hx6 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261016</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>THAI YOOWON ELECTRONICS CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>EVAPORATOR</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>0</v>
@@ -1517,22 +1517,22 @@
     <row r="13" ht="13" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902363</t>
+          <t>HASLS22261000205</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>HAB</t>
+          <t>SWAT</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>202610282300</t>
+          <t>202611050900</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>JPIYM</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x5 </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1558,27 +1558,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>AGC VINYTHAI PUBLIC COMPANY LIMITED</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>PVC RESIN</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>NEW CNTR, GRADE A</t>
+          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>0</v>
@@ -1602,22 +1602,22 @@
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902504</t>
+          <t>HASLS22261000303</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>HAHM</t>
+          <t>SWDN</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2612N</t>
+          <t>2611N</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>202610280700</t>
+          <t>202611020200</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1628,27 +1628,27 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>VNSGN</t>
+          <t>KRINC</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 20'x1 </t>
+          <t xml:space="preserve">40Hx1 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>TIETEX ASIA LIMITED</t>
+          <t>SRI TRANG GLOVES (THAILAND) PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>POLYESTER</t>
+          <t xml:space="preserve">GLOVES </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
@@ -1687,22 +1687,22 @@
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HASLS22260902549</t>
+          <t>HASLS22261000344</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>202611041600</t>
+          <t>202610271500</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1713,42 +1713,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>CNSHK</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20260926</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>THAIXING CIRCUITS CO., LTD.</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>MULTILAYER PRINTED CIRCUIT BOARD</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="2" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000008</t>
+          <t>HASLS22261000345</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>202610271900</t>
+          <t>202610271500</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>KRPUS</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>UBE CHEMICALS (ASIA) PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>POLYAMIDE RESIN</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Sound and Clean</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
@@ -1857,22 +1857,22 @@
     <row r="17" ht="13" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000040</t>
+          <t>HASLS22261000347</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>KMSU</t>
+          <t>HMVY</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2608S</t>
+          <t>2609N</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>202611012100</t>
+          <t>202610271500</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>IDJKT</t>
+          <t>JPNGO</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1893,22 +1893,22 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>QUAKER HOUGHTON (THAILAND) CO., LTD.</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>QUAKERCOOL 2770 PLUS</t>
+          <t>RESIN</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>DG22GPx1 (CLS 9 / UN 3082)</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
@@ -1942,7 +1942,7 @@
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000171</t>
+          <t>HASLS22261000348</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202610282300</t>
+          <t>202610290200</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1968,22 +1968,22 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx1 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1993,17 +1993,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" s="2" t="n">
         <v>0</v>
@@ -2027,7 +2027,7 @@
     <row r="19" ht="13" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000172</t>
+          <t>HASLS22261000349</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>202610282300</t>
+          <t>202610290200</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -2053,22 +2053,22 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40Hx6 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20261016</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2078,17 +2078,17 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P19" s="2" t="n">
         <v>0</v>
@@ -2112,22 +2112,22 @@
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000205</t>
+          <t>HASLS22261000411</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SWAT</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2611N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>202611041600</t>
+          <t>202611082100</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -2138,22 +2138,22 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>JPIYM</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x5 </t>
+          <t xml:space="preserve">20'x1 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20261021</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
+          <t>SIAM POLYETHYLENE CO., LTD.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2163,11 +2163,11 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>*** REQ. GOOD &amp; CLEAN  CONT. .( NO SMELL)  ***</t>
+          <t>1X20' SEABULK</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -2197,22 +2197,22 @@
     <row r="21" ht="13" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000344</t>
+          <t>HASLS22261000414</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>SWSP</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2610N</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>202610271900</t>
+          <t>202611082100</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPYKK</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2282,22 +2282,22 @@
     <row r="22" ht="13" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000345</t>
+          <t>HASLS22261000603</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>SWIC</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>202610271900</t>
+          <t>202611101600</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -2308,22 +2308,22 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPUKB</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x7 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2333,11 +2333,11 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>SEA BULK CTNR // SURVEY DD.21/10</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N22" s="2" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000347</t>
+          <t>HASLS22261001009</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>SWBT</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2618N</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>202610271900</t>
+          <t>202611082000</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -2393,22 +2393,22 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>JPNGO</t>
+          <t>JPYOK</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">20'x2 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2418,11 +2418,11 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>SEA BULK CTNR // SURVEY DD.21/10</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
     <row r="24" ht="13" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000348</t>
+          <t>HASLS22261001467</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>202610282300</t>
+          <t>202610290200</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -2478,42 +2478,42 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>CNSHA</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261021</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>FUZIN PLASTIC CO.,LTD.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>PE RECYCLE PELLET</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>RQST CNTR 32.5 TONS // 40'HQ</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P24" s="2" t="n">
         <v>0</v>
@@ -2537,7 +2537,7 @@
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000349</t>
+          <t>HASLS22261001562</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>202610282300</t>
+          <t>202610290200</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -2563,42 +2563,42 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>JPYKK</t>
+          <t>KRPUS</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
+          <t>THAILON TECHNO FIBER LIMITED</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>RESIN</t>
+          <t>NYLON YARN</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1X20' SEABULK</t>
+          <t>GOOD AND CLEAN CONTAINER</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P25" s="2" t="n">
         <v>0</v>
@@ -2622,22 +2622,22 @@
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000396</t>
+          <t>HASLS22261001797</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>HMVY</t>
+          <t>HAHM</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2609N</t>
+          <t>2612N</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>202610271900</t>
+          <t>202610280700</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -2648,42 +2648,42 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>CNSHA</t>
+          <t>VNSGN</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20'x1 </t>
+          <t xml:space="preserve">40Hx2 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20261020</t>
+          <t>20261022</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>DAECHANG TRADING (THAILAND) CO.,LTD.</t>
+          <t>XTREME ELECTRONICS CO., LTD</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>BRASS ROD</t>
+          <t>LED TV COOCAA</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>REQUEST GOOD &amp; CLEAN CONTAINER / WITHOUT HOLE</t>
+          <t>GOOD AND CLEAN CONTAINER, NO LEAK NO HOLE AND NO SMELL</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P26" s="2" t="n">
         <v>0</v>
@@ -2705,1805 +2705,104 @@
       </c>
     </row>
     <row r="27" ht="13" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000411</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SWSP</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>202611041200</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>JPYKK</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>1X20' SEABULK</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="13" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000414</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SWSP</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>202611041200</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>JPYKK</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>20261019</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>SIAM POLYETHYLENE CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1X20' SEABULK</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="13" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000491</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>KMBK</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>202610262300</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x2 </t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>BEN TECH CHEMICAL CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>DYEING AUXILIARY FOR TEXTILE</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CTNR</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" s="2" t="n">
-        <v>0</v>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3">
+        <f>SUM(M2:M26)</f>
+        <v/>
+      </c>
+      <c r="N27" s="3">
+        <f>SUM(N2:N26)</f>
+        <v/>
+      </c>
+      <c r="O27" s="3">
+        <f>SUM(O2:O26)</f>
+        <v/>
+      </c>
+      <c r="P27" s="3">
+        <f>SUM(P2:P26)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="3">
+        <f>SUM(Q2:Q26)</f>
+        <v/>
+      </c>
+      <c r="R27" s="3">
+        <f>SUM(R2:R26)</f>
+        <v/>
+      </c>
+      <c r="S27" s="3">
+        <f>SUM(S2:S26)</f>
+        <v/>
+      </c>
+      <c r="T27" s="3">
+        <f>SUM(T2:T26)</f>
+        <v/>
+      </c>
+      <c r="U27" s="3">
+        <f>SUM(U2:U26)</f>
+        <v/>
       </c>
     </row>
     <row r="30" ht="13" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000603</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>SWIC</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>202611101600</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>JPUKB</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x7 </t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>SEA BULK CTNR // SURVEY DD.21/10</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="2" t="n">
-        <v>0</v>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Pickup Name</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Number of Records</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Total Balance</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HASLS22261000650</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>DJCF</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>0153N</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>202611031700</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>KRPTK</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx3 </t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>THAI SAMSUNG ELECTRONICS CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>AIR CONDTIONER</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>No containers with cut and patch marks inside*
-GOOD CLEAN CONTIANER NO BLEAM (ELECTRONICS GOODS)</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" s="2" t="n">
-        <v>0</v>
+          <t>PW DEPOT CO., LTD.</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="32" ht="13" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000813</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>KMGY</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>202610241900</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx12 </t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>20261017</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>KURARAY CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>GENESTAR</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>GOOD DRY AND CLEAN CONTAINER.</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="13" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000849</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>202610251500</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>AJ PLAST PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>BOPP FILM</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>Request container upgrade 32.5 tons Dry ,clean and good condition containers (grade A for food grade)</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="13" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000905</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>KMBK</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>202610262300</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x5 </t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>XIAO XIANG CHEMICAL INDUSTRY (THAILAND) CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>ZINC INGOT</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="13" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261000969</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>HAB</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>202610282300</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx3 </t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="13" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261001009</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>SWBT</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>2618N</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>202611082000</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>JPYOK</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x2 </t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>SEA BULK CTNR // SURVEY DD.21/10</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="13" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261001118</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>HMVY</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>2609N</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>202610271900</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx4 </t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>20261020</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>FIRST MATERIAL SCIENCE (THAILAND) CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ETHYLENE VINYL ACETATE RESIN </t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>REQUEST GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" ht="13" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261001236</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>KMBK</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>202610262300</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>KURARAY GC ADVANCED MATERIALS CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>GENESTAR</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>REQ. GOOD, CLEAN &amp; DRY GRADE A CONTAINER.</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="13" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261001455</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>HAHM</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>202610280700</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>VNSGN</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx7 </t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>VANACHAI GROUP PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>PARTICLE BOARD</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>RQST CNGR 32.5 TONS</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="P39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="13" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261001467</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>HAB</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>202610282300</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>FUZIN PLASTIC CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>PE RECYCLE PELLET</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>RQST CNTR 32.5 TONS // 40'HQ</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="13" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261001615</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>HAB</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>202610282300</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx6 </t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>RQST GOOD &amp; CLEAN CNTR</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="P41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="13" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261001616</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>HAB</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>202610282300</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx4 </t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>RQST GOOD &amp; CLEAN CNTR</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="13" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261001632</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>HAB</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>202610282300</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx30 </t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>SHUN YI INTERNATIONAL TRADING CO., LTD.</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>PAPER PULP</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>RQST CNTR 32.5 TONS // 40'HQ</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="P43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="13" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261001704</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>SWDN</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>2611N</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>202611020200</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>HKHKG</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx1 </t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>UMC ELECTRONICS (THAILAND) LTD.</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> PCBA (8537.20.29)</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>good and clean container</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="13" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261001710</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>HAB</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>2612N</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>202610282300</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>CNSHA</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40Hx2 </t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>PTT GLOBAL CHEMICAL PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>RESIN</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="13" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>HASLS22261001714</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>SWMM</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>2610N</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>202610251500</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>THLCH</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>KRPUS</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20'x1 </t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>20261021</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>ALUCON PUBLIC COMPANY LIMITED</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>ALUMINIUM CANS (EMPTY)</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>GOOD AND CLEAN CONTAINER</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="13" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="n"/>
-      <c r="F47" s="3" t="n"/>
-      <c r="G47" s="3" t="n"/>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
-      <c r="J47" s="3" t="n"/>
-      <c r="K47" s="3" t="n"/>
-      <c r="L47" s="3" t="n"/>
-      <c r="M47" s="3">
-        <f>SUM(M2:M46)</f>
-        <v/>
-      </c>
-      <c r="N47" s="3">
-        <f>SUM(N2:N46)</f>
-        <v/>
-      </c>
-      <c r="O47" s="3">
-        <f>SUM(O2:O46)</f>
-        <v/>
-      </c>
-      <c r="P47" s="3">
-        <f>SUM(P2:P46)</f>
-        <v/>
-      </c>
-      <c r="Q47" s="3">
-        <f>SUM(Q2:Q46)</f>
-        <v/>
-      </c>
-      <c r="R47" s="3">
-        <f>SUM(R2:R46)</f>
-        <v/>
-      </c>
-      <c r="S47" s="3">
-        <f>SUM(S2:S46)</f>
-        <v/>
-      </c>
-      <c r="T47" s="3">
-        <f>SUM(T2:T46)</f>
-        <v/>
-      </c>
-      <c r="U47" s="3">
-        <f>SUM(U2:U46)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="13" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Pickup Name</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Number of Records</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Total Balance</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="13" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>PW DEPOT CO., LTD.</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="52" ht="13" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>สรุปยอดบุ๊คทั้งหมด</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>134</v>
+      <c r="B32" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U46"/>
+  <autoFilter ref="A1:U26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>